--- a/database/event/4574/event_4574_evp_summary.xlsx
+++ b/database/event/4574/event_4574_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.5039</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6719</v>
+        <v>3.5929</v>
       </c>
       <c r="E2" t="n">
         <v>10.1325</v>
@@ -548,7 +548,7 @@
         <v>2.8969</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9628</v>
+        <v>2.8936</v>
       </c>
       <c r="E3" t="n">
         <v>8.3772</v>
@@ -594,7 +594,7 @@
         <v>2.4743</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4691</v>
+        <v>2.4066</v>
       </c>
       <c r="E4" t="n">
         <v>7.1549</v>
@@ -640,7 +640,7 @@
         <v>1.801</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6826</v>
+        <v>1.631</v>
       </c>
       <c r="E5" t="n">
         <v>5.2081</v>
@@ -686,7 +686,7 @@
         <v>1.7247</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5935</v>
+        <v>1.5431</v>
       </c>
       <c r="E6" t="n">
         <v>4.9875</v>
@@ -732,7 +732,7 @@
         <v>1.5741</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4175</v>
+        <v>1.3696</v>
       </c>
       <c r="E7" t="n">
         <v>4.552</v>
@@ -778,7 +778,7 @@
         <v>1.5695</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4122</v>
+        <v>1.3643</v>
       </c>
       <c r="E8" t="n">
         <v>4.5387</v>
@@ -824,7 +824,7 @@
         <v>1.5405</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3782</v>
+        <v>1.3308</v>
       </c>
       <c r="E9" t="n">
         <v>4.4546</v>
@@ -870,7 +870,7 @@
         <v>1.4981</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3288</v>
+        <v>1.282</v>
       </c>
       <c r="E10" t="n">
         <v>4.3322</v>
@@ -916,7 +916,7 @@
         <v>1.4946</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3246</v>
+        <v>1.2779</v>
       </c>
       <c r="E11" t="n">
         <v>4.3219</v>
@@ -962,7 +962,7 @@
         <v>1.3314</v>
       </c>
       <c r="D12" t="n">
-        <v>1.134</v>
+        <v>1.0899</v>
       </c>
       <c r="E12" t="n">
         <v>3.85</v>
@@ -1008,7 +1008,7 @@
         <v>1.07</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8286</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="E13" t="n">
         <v>3.0941</v>
@@ -1054,7 +1054,7 @@
         <v>0.9199000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6532</v>
+        <v>0.6158</v>
       </c>
       <c r="E14" t="n">
         <v>2.66</v>
@@ -1100,7 +1100,7 @@
         <v>0.6676</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3585</v>
+        <v>0.3252</v>
       </c>
       <c r="E15" t="n">
         <v>1.9305</v>
@@ -1146,7 +1146,7 @@
         <v>0.6546999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3434</v>
+        <v>0.3103</v>
       </c>
       <c r="E16" t="n">
         <v>1.8931</v>
@@ -1192,7 +1192,7 @@
         <v>0.5809</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2572</v>
+        <v>0.2253</v>
       </c>
       <c r="E17" t="n">
         <v>1.6797</v>
@@ -1238,7 +1238,7 @@
         <v>0.531</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1989</v>
+        <v>0.1678</v>
       </c>
       <c r="E18" t="n">
         <v>1.5355</v>
@@ -1284,7 +1284,7 @@
         <v>0.5263</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1934</v>
+        <v>0.1624</v>
       </c>
       <c r="E19" t="n">
         <v>1.5218</v>
@@ -1330,7 +1330,7 @@
         <v>0.5149</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1801</v>
+        <v>0.1493</v>
       </c>
       <c r="E20" t="n">
         <v>1.4889</v>
@@ -1376,7 +1376,7 @@
         <v>0.3119</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.057</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="E21" t="n">
         <v>0.902</v>
@@ -1422,7 +1422,7 @@
         <v>0.2502</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1291</v>
+        <v>-0.1557</v>
       </c>
       <c r="E22" t="n">
         <v>0.7235</v>
@@ -1468,7 +1468,7 @@
         <v>0.191</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1982</v>
+        <v>-0.2238</v>
       </c>
       <c r="E23" t="n">
         <v>0.5524</v>
@@ -1514,7 +1514,7 @@
         <v>0.1799</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2113</v>
+        <v>-0.2367</v>
       </c>
       <c r="E24" t="n">
         <v>0.5201</v>
@@ -1560,7 +1560,7 @@
         <v>0.1328</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2663</v>
+        <v>-0.291</v>
       </c>
       <c r="E25" t="n">
         <v>0.3839</v>
@@ -1606,7 +1606,7 @@
         <v>0.1104</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2924</v>
+        <v>-0.3167</v>
       </c>
       <c r="E26" t="n">
         <v>0.3193</v>
@@ -1652,7 +1652,7 @@
         <v>0.0422</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.372</v>
+        <v>-0.3953</v>
       </c>
       <c r="E27" t="n">
         <v>0.1221</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0251</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4507</v>
+        <v>-0.4728</v>
       </c>
       <c r="E28" t="n">
         <v>-0.0725</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0518</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4818</v>
+        <v>-0.5036</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1497</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1056</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5447</v>
+        <v>-0.5655</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3053</v>
@@ -1836,7 +1836,7 @@
         <v>-0.12</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5615</v>
+        <v>-0.5821</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3469</v>
@@ -1882,7 +1882,7 @@
         <v>-0.13</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5732</v>
+        <v>-0.5937</v>
       </c>
       <c r="E32" t="n">
         <v>-0.3759</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1803</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.632</v>
+        <v>-0.6516</v>
       </c>
       <c r="E33" t="n">
         <v>-0.5213</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1805</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6323</v>
+        <v>-0.6519</v>
       </c>
       <c r="E34" t="n">
         <v>-0.5221</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2739</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7413</v>
+        <v>-0.7594</v>
       </c>
       <c r="E35" t="n">
         <v>-0.792</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2818</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7506</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8149</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3089</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7822</v>
+        <v>-0.7998</v>
       </c>
       <c r="E37" t="n">
         <v>-0.8932</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3408</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8194</v>
+        <v>-0.8365</v>
       </c>
       <c r="E38" t="n">
         <v>-0.9854000000000001</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3458</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E39" t="n">
         <v>-1</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6121</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1364</v>
+        <v>-1.1491</v>
       </c>
       <c r="E40" t="n">
         <v>-1.77</v>
@@ -2296,7 +2296,7 @@
         <v>-0.8789</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4481</v>
+        <v>-1.4565</v>
       </c>
       <c r="E41" t="n">
         <v>-2.5416</v>
@@ -2342,7 +2342,7 @@
         <v>-1.2683</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.903</v>
+        <v>-1.9051</v>
       </c>
       <c r="E42" t="n">
         <v>-3.6676</v>

--- a/database/event/4574/event_4574_evp_summary.xlsx
+++ b/database/event/4574/event_4574_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.1325</v>
+        <v>8.830500000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5039</v>
+        <v>3.0537</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5929</v>
+        <v>3.3485</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1325</v>
+        <v>8.830500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1993</v>
+        <v>3.6087</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9333</v>
+        <v>5.2219</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3341</v>
+        <v>7.2283</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5129</v>
+        <v>3.7584</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9333</v>
+        <v>5.2219</v>
       </c>
       <c r="K2" t="n">
         <v>122</v>
@@ -529,7 +529,7 @@
         <v>119</v>
       </c>
       <c r="M2" t="n">
-        <v>9.446200000000001</v>
+        <v>8.9803</v>
       </c>
       <c r="N2" t="n">
         <v>241</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.3772</v>
+        <v>7.4747</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8969</v>
+        <v>2.5848</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8936</v>
+        <v>2.7364</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3772</v>
+        <v>7.4747</v>
       </c>
       <c r="F3" t="n">
-        <v>3.846</v>
+        <v>3.4359</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5312</v>
+        <v>4.0388</v>
       </c>
       <c r="H3" t="n">
-        <v>3.846</v>
+        <v>6.6196</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1173</v>
+        <v>3.4419</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5312</v>
+        <v>4.0388</v>
       </c>
       <c r="K3" t="n">
         <v>122</v>
@@ -575,7 +575,7 @@
         <v>119</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6485</v>
+        <v>7.480700000000001</v>
       </c>
       <c r="N3" t="n">
         <v>241</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1549</v>
+        <v>7.2714</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4743</v>
+        <v>2.5145</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4066</v>
+        <v>2.6447</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1549</v>
+        <v>7.2714</v>
       </c>
       <c r="F4" t="n">
-        <v>2.245</v>
+        <v>2.9012</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9099</v>
+        <v>4.3702</v>
       </c>
       <c r="H4" t="n">
-        <v>2.245</v>
+        <v>4.7358</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8196</v>
+        <v>2.4624</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9099</v>
+        <v>4.3702</v>
       </c>
       <c r="K4" t="n">
         <v>122</v>
@@ -621,7 +621,7 @@
         <v>119</v>
       </c>
       <c r="M4" t="n">
-        <v>6.729500000000001</v>
+        <v>6.832599999999999</v>
       </c>
       <c r="N4" t="n">
         <v>241</v>
@@ -630,185 +630,185 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2081</v>
+        <v>5.1707</v>
       </c>
       <c r="C5" t="n">
-        <v>1.801</v>
+        <v>1.7881</v>
       </c>
       <c r="D5" t="n">
-        <v>1.631</v>
+        <v>1.6963</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2081</v>
+        <v>5.1707</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3925</v>
+        <v>1.6628</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8156</v>
+        <v>3.5079</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1116</v>
+        <v>1.6628</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1431</v>
+        <v>0.8646</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8156</v>
+        <v>3.5079</v>
       </c>
       <c r="K5" t="n">
-        <v>210</v>
+        <v>122</v>
       </c>
       <c r="L5" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="M5" t="n">
-        <v>4.958699999999999</v>
+        <v>4.3725</v>
       </c>
       <c r="N5" t="n">
-        <v>279</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9875</v>
+        <v>4.7385</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7247</v>
+        <v>1.6386</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5431</v>
+        <v>1.5012</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9875</v>
+        <v>4.7385</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8013</v>
+        <v>4.0615</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1862</v>
+        <v>0.677</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8013</v>
+        <v>8.824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6495</v>
+        <v>4.5881</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1862</v>
+        <v>0.677</v>
       </c>
       <c r="K6" t="n">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="L6" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8357</v>
+        <v>5.2651</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.552</v>
+        <v>4.4855</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5741</v>
+        <v>1.5511</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3696</v>
+        <v>1.387</v>
       </c>
       <c r="E7" t="n">
-        <v>4.552</v>
+        <v>4.4855</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2057</v>
+        <v>3.7282</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3463</v>
+        <v>0.7573</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3601</v>
+        <v>7.6495</v>
       </c>
       <c r="I7" t="n">
-        <v>3.534</v>
+        <v>3.9774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3463</v>
+        <v>0.7573</v>
       </c>
       <c r="K7" t="n">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="L7" t="n">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8803</v>
+        <v>4.7347</v>
       </c>
       <c r="N7" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5387</v>
+        <v>4.2834</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5695</v>
+        <v>1.4813</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3643</v>
+        <v>1.2957</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5387</v>
+        <v>4.2834</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2248</v>
+        <v>3.9495</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3139</v>
+        <v>0.3339</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4369</v>
+        <v>8.429399999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5962</v>
+        <v>4.3829</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3139</v>
+        <v>0.3339</v>
       </c>
       <c r="K8" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="L8" t="n">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9101</v>
+        <v>4.7168</v>
       </c>
       <c r="N8" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4546</v>
+        <v>4.1476</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5405</v>
+        <v>1.4343</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3308</v>
+        <v>1.2344</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4546</v>
+        <v>4.1476</v>
       </c>
       <c r="F9" t="n">
-        <v>4.35</v>
+        <v>3.981</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1046</v>
+        <v>0.1666</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9404</v>
+        <v>8.5404</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0044</v>
+        <v>4.4406</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1046</v>
+        <v>0.1666</v>
       </c>
       <c r="K9" t="n">
         <v>182</v>
@@ -851,7 +851,7 @@
         <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>4.109</v>
+        <v>4.6072</v>
       </c>
       <c r="N9" t="n">
         <v>234</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3322</v>
+        <v>4.1303</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4981</v>
+        <v>1.4283</v>
       </c>
       <c r="D10" t="n">
-        <v>1.282</v>
+        <v>1.2266</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3322</v>
+        <v>4.1303</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2419</v>
+        <v>2.7056</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09030000000000001</v>
+        <v>1.4247</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5055</v>
+        <v>4.0465</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6518</v>
+        <v>2.104</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09030000000000001</v>
+        <v>1.4247</v>
       </c>
       <c r="K10" t="n">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="L10" t="n">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7421</v>
+        <v>3.5287</v>
       </c>
       <c r="N10" t="n">
-        <v>279</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.3219</v>
+        <v>4.0378</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4946</v>
+        <v>1.3963</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2779</v>
+        <v>1.1849</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3219</v>
+        <v>4.0378</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4953</v>
+        <v>4.0106</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8266</v>
+        <v>0.0272</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4953</v>
+        <v>8.644600000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0225</v>
+        <v>4.4948</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8266</v>
+        <v>0.0272</v>
       </c>
       <c r="K11" t="n">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="L11" t="n">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8491</v>
+        <v>4.521999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>247</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.85</v>
+        <v>3.9229</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3314</v>
+        <v>1.3566</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0899</v>
+        <v>1.133</v>
       </c>
       <c r="E12" t="n">
-        <v>3.85</v>
+        <v>3.9229</v>
       </c>
       <c r="F12" t="n">
-        <v>2.472</v>
+        <v>2.6474</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3781</v>
+        <v>1.2755</v>
       </c>
       <c r="H12" t="n">
-        <v>2.472</v>
+        <v>3.8413</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0036</v>
+        <v>1.9973</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3781</v>
+        <v>1.2755</v>
       </c>
       <c r="K12" t="n">
         <v>111</v>
@@ -989,7 +989,7 @@
         <v>136</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3817</v>
+        <v>3.2728</v>
       </c>
       <c r="N12" t="n">
         <v>247</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0941</v>
+        <v>3.1723</v>
       </c>
       <c r="C13" t="n">
-        <v>1.07</v>
+        <v>1.097</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7941</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0941</v>
+        <v>3.1723</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9733</v>
+        <v>2.4913</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1209</v>
+        <v>0.681</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9733</v>
+        <v>3.2914</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5994</v>
+        <v>1.7114</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1209</v>
+        <v>0.681</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1035,7 +1035,7 @@
         <v>136</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7203</v>
+        <v>2.3924</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.66</v>
+        <v>2.6545</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6158</v>
+        <v>0.5604</v>
       </c>
       <c r="E14" t="n">
-        <v>2.66</v>
+        <v>2.6545</v>
       </c>
       <c r="F14" t="n">
-        <v>2.66</v>
+        <v>2.6545</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.6545</v>
       </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>2.6545</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.66</v>
+        <v>2.6545</v>
       </c>
       <c r="N14" t="n">
         <v>207</v>
@@ -1090,78 +1090,78 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9305</v>
+        <v>2.4568</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6676</v>
+        <v>0.8496</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3252</v>
+        <v>0.4711</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9305</v>
+        <v>2.4568</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9305</v>
+        <v>2.252</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.2048</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9305</v>
+        <v>2.4485</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9305</v>
+        <v>1.2731</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2048</v>
       </c>
       <c r="K15" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9305</v>
+        <v>1.4779</v>
       </c>
       <c r="N15" t="n">
-        <v>189</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8931</v>
+        <v>2.1974</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.7599</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3103</v>
+        <v>0.354</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8931</v>
+        <v>2.1974</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8931</v>
+        <v>2.1974</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8931</v>
+        <v>2.1974</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8931</v>
+        <v>2.1974</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8931</v>
+        <v>2.1974</v>
       </c>
       <c r="N16" t="n">
         <v>189</v>
@@ -1182,357 +1182,357 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6797</v>
+        <v>2.1871</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5809</v>
+        <v>0.7563</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2253</v>
+        <v>0.3494</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6797</v>
+        <v>2.1871</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6797</v>
+        <v>2.1871</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6797</v>
+        <v>2.1871</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6797</v>
+        <v>2.1871</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6797</v>
+        <v>2.1871</v>
       </c>
       <c r="N17" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5355</v>
+        <v>2.1213</v>
       </c>
       <c r="C18" t="n">
-        <v>0.531</v>
+        <v>0.7336</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1678</v>
+        <v>0.3196</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5355</v>
+        <v>2.1213</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5355</v>
+        <v>2.1213</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5355</v>
+        <v>2.1213</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5355</v>
+        <v>2.1213</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5355</v>
+        <v>2.1213</v>
       </c>
       <c r="N18" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5218</v>
+        <v>2.0871</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5263</v>
+        <v>0.7217</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1624</v>
+        <v>0.3042</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5218</v>
+        <v>2.0871</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5218</v>
+        <v>2.4174</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.3303</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5218</v>
+        <v>3.0312</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5218</v>
+        <v>1.5761</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.3303</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5218</v>
+        <v>1.2458</v>
       </c>
       <c r="N19" t="n">
-        <v>207</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4889</v>
+        <v>2.071</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5149</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1493</v>
+        <v>0.2969</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4889</v>
+        <v>2.071</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5208</v>
+        <v>2.385</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0319</v>
+        <v>-0.314</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5208</v>
+        <v>2.9168</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2326</v>
+        <v>1.5166</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0319</v>
+        <v>-0.314</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L20" t="n">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2007</v>
+        <v>1.2026</v>
       </c>
       <c r="N20" t="n">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.902</v>
+        <v>1.9378</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3119</v>
+        <v>0.6701</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08459999999999999</v>
+        <v>0.2368</v>
       </c>
       <c r="E21" t="n">
-        <v>0.902</v>
+        <v>1.9378</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2994</v>
+        <v>1.9378</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3974</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2994</v>
+        <v>1.9378</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8637</v>
+        <v>1.9378</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3974</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="L21" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4662999999999999</v>
+        <v>1.9378</v>
       </c>
       <c r="N21" t="n">
-        <v>247</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7235</v>
+        <v>1.7614</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2502</v>
+        <v>0.6091</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1557</v>
+        <v>0.1572</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7235</v>
+        <v>1.7614</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2424</v>
+        <v>1.7614</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5189</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2424</v>
+        <v>1.7614</v>
       </c>
       <c r="I22" t="n">
-        <v>1.007</v>
+        <v>1.7614</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5189</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="L22" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4880999999999999</v>
+        <v>1.7614</v>
       </c>
       <c r="N22" t="n">
-        <v>234</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5524</v>
+        <v>1.6502</v>
       </c>
       <c r="C23" t="n">
-        <v>0.191</v>
+        <v>0.5707</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2238</v>
+        <v>0.107</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5524</v>
+        <v>1.6502</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5524</v>
+        <v>2.4295</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.7793</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5524</v>
+        <v>3.0737</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5524</v>
+        <v>1.5982</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.7793</v>
       </c>
       <c r="K23" t="n">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5524</v>
+        <v>0.8189000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>104</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5201</v>
+        <v>1.4635</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1799</v>
+        <v>0.5061</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2367</v>
+        <v>0.0227</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5201</v>
+        <v>1.4635</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9489</v>
+        <v>2.3131</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4288</v>
+        <v>-0.8496</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9489</v>
+        <v>2.6635</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7691</v>
+        <v>1.3849</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4288</v>
+        <v>-0.8496</v>
       </c>
       <c r="K24" t="n">
         <v>210</v>
@@ -1541,7 +1541,7 @@
         <v>69</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3403</v>
+        <v>0.5353</v>
       </c>
       <c r="N24" t="n">
         <v>279</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NaToSaphiX</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3839</v>
+        <v>1.4394</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1328</v>
+        <v>0.4978</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.291</v>
+        <v>0.0118</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3839</v>
+        <v>1.4394</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3839</v>
+        <v>2.612</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1.1726</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3839</v>
+        <v>3.7167</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3839</v>
+        <v>1.9325</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1.1726</v>
       </c>
       <c r="K25" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3839</v>
+        <v>0.7599</v>
       </c>
       <c r="N25" t="n">
-        <v>189</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3193</v>
+        <v>1.0795</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1104</v>
+        <v>0.3733</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3167</v>
+        <v>-0.1507</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3193</v>
+        <v>1.0795</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3193</v>
+        <v>1.0795</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3193</v>
+        <v>1.0795</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0693</v>
+        <v>1.0795</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06929999999999992</v>
+        <v>1.0795</v>
       </c>
       <c r="N26" t="n">
-        <v>234</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>NaToSaphiX</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1221</v>
+        <v>0.7421</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0422</v>
+        <v>0.2566</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3953</v>
+        <v>-0.303</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1221</v>
+        <v>0.7421</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1221</v>
+        <v>0.7421</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1221</v>
+        <v>0.7421</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9095</v>
+        <v>0.7421</v>
       </c>
       <c r="J27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="L27" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.09050000000000002</v>
+        <v>0.7421</v>
       </c>
       <c r="N27" t="n">
-        <v>279</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0725</v>
+        <v>0.3125</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0251</v>
+        <v>0.1081</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4728</v>
+        <v>-0.4969</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0725</v>
+        <v>0.3125</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0725</v>
+        <v>0.3125</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0725</v>
+        <v>0.3125</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0725</v>
+        <v>0.3125</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0725</v>
+        <v>0.3125</v>
       </c>
       <c r="N28" t="n">
         <v>104</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1497</v>
+        <v>0.1362</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0518</v>
+        <v>0.0471</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5036</v>
+        <v>-0.5765</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1497</v>
+        <v>0.1362</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1497</v>
+        <v>0.1362</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1497</v>
+        <v>0.1362</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1497</v>
+        <v>0.1362</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1497</v>
+        <v>0.1362</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1780,78 +1780,78 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3053</v>
+        <v>-0.0164</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1056</v>
+        <v>-0.0057</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5655</v>
+        <v>-0.6454</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3053</v>
+        <v>-0.0164</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3053</v>
+        <v>-0.0164</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3053</v>
+        <v>-0.0164</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3053</v>
+        <v>-0.0164</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3053</v>
+        <v>-0.0164</v>
       </c>
       <c r="N30" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3469</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.12</v>
+        <v>-0.0225</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5821</v>
+        <v>-0.6674</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3469</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3469</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3469</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3469</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3469</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>207</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3759</v>
+        <v>-0.1912</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.13</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5937</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3759</v>
+        <v>-0.1912</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3759</v>
+        <v>-0.1912</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3759</v>
+        <v>-0.1912</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3759</v>
+        <v>-0.1912</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3759</v>
+        <v>-0.1912</v>
       </c>
       <c r="N32" t="n">
-        <v>207</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5213</v>
+        <v>-0.225</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1803</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6516</v>
+        <v>-0.7396</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5213</v>
+        <v>-0.225</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5213</v>
+        <v>-0.225</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5213</v>
+        <v>-0.225</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5213</v>
+        <v>-0.225</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5213</v>
+        <v>-0.225</v>
       </c>
       <c r="N33" t="n">
-        <v>104</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5221</v>
+        <v>-0.2575</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1805</v>
+        <v>-0.089</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6519</v>
+        <v>-0.7543</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5221</v>
+        <v>-0.2575</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5221</v>
+        <v>-0.2575</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5221</v>
+        <v>-0.2575</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5221</v>
+        <v>-0.2575</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5221</v>
+        <v>-0.2575</v>
       </c>
       <c r="N34" t="n">
         <v>125</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.792</v>
+        <v>-0.4408</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2739</v>
+        <v>-0.1524</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7594</v>
+        <v>-0.837</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.792</v>
+        <v>-0.4408</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.792</v>
+        <v>-0.4408</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.792</v>
+        <v>-0.4408</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.792</v>
+        <v>-0.4408</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.792</v>
+        <v>-0.4408</v>
       </c>
       <c r="N35" t="n">
         <v>125</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8149</v>
+        <v>-0.4762</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2818</v>
+        <v>-0.1647</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.853</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8149</v>
+        <v>-0.4762</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8149</v>
+        <v>-0.4762</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8149</v>
+        <v>-0.4762</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8149</v>
+        <v>-0.4762</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8149</v>
+        <v>-0.4762</v>
       </c>
       <c r="N36" t="n">
         <v>125</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8932</v>
+        <v>-0.5345</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3089</v>
+        <v>-0.1848</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7998</v>
+        <v>-0.8793</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8932</v>
+        <v>-0.5345</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8932</v>
+        <v>-0.5345</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8932</v>
+        <v>-0.5345</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8932</v>
+        <v>-0.5345</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8932</v>
+        <v>-0.5345</v>
       </c>
       <c r="N37" t="n">
         <v>104</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.5773</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3408</v>
+        <v>-0.1996</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8365</v>
+        <v>-0.8986</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.5773</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.5773</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.5773</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.5773</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.5773</v>
       </c>
       <c r="N38" t="n">
         <v>86</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1</v>
+        <v>-0.9405</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3458</v>
+        <v>-0.3252</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8423</v>
+        <v>-1.0626</v>
       </c>
       <c r="E39" t="n">
-        <v>-1</v>
+        <v>-0.9405</v>
       </c>
       <c r="F39" t="n">
-        <v>-1</v>
+        <v>-0.9405</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1</v>
+        <v>-0.9405</v>
       </c>
       <c r="I39" t="n">
-        <v>-1</v>
+        <v>-0.9405</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1</v>
+        <v>-0.9405</v>
       </c>
       <c r="N39" t="n">
         <v>39</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.77</v>
+        <v>-1.2253</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6121</v>
+        <v>-0.4237</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1491</v>
+        <v>-1.1912</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.77</v>
+        <v>-1.2253</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.77</v>
+        <v>-1.2253</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.77</v>
+        <v>-1.2253</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.77</v>
+        <v>-1.2253</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.77</v>
+        <v>-1.2253</v>
       </c>
       <c r="N40" t="n">
         <v>104</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5416</v>
+        <v>-1.887</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8789</v>
+        <v>-0.6525</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4565</v>
+        <v>-1.4899</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5416</v>
+        <v>-1.887</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6877</v>
+        <v>-1.3259</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8539</v>
+        <v>-0.5611</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6877</v>
+        <v>-1.3259</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3679</v>
+        <v>-0.6894</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8539</v>
+        <v>-0.5611</v>
       </c>
       <c r="K41" t="n">
         <v>182</v>
@@ -2323,7 +2323,7 @@
         <v>52</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2218</v>
+        <v>-1.2505</v>
       </c>
       <c r="N41" t="n">
         <v>234</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-3.6676</v>
+        <v>-3.3796</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.2683</v>
+        <v>-1.1687</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.9051</v>
+        <v>-2.1637</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.6676</v>
+        <v>-3.3796</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.6676</v>
+        <v>-2.3796</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.6676</v>
+        <v>-2.3796</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.1622</v>
+        <v>-1.2373</v>
       </c>
       <c r="J42" t="n">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>69</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.1622</v>
+        <v>-2.2373</v>
       </c>
       <c r="N42" t="n">
         <v>279</v>
@@ -2475,10 +2475,10 @@
         <v>0.83</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1485</v>
+        <v>-0.1436</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.673</v>
+        <v>-2.5848</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2274</v>
+        <v>-0.1997</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.0932</v>
+        <v>-3.5946</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.533</v>
+        <v>-0.3759</v>
       </c>
       <c r="J4" t="n">
-        <v>-9.593999999999999</v>
+        <v>-6.7662</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.58</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5667</v>
+        <v>-0.394</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.2006</v>
+        <v>-7.092</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.3</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.6587</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.9938</v>
+        <v>-11.8566</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.94</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8395</v>
+        <v>1.5706</v>
       </c>
       <c r="J7" t="n">
-        <v>33.111</v>
+        <v>28.2708</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.93</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8227</v>
+        <v>1.5598</v>
       </c>
       <c r="J8" t="n">
-        <v>32.8086</v>
+        <v>28.0764</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.53</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0409</v>
+        <v>1.1171</v>
       </c>
       <c r="J9" t="n">
-        <v>18.7362</v>
+        <v>20.1078</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.46</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9009</v>
+        <v>1.031</v>
       </c>
       <c r="J10" t="n">
-        <v>16.2162</v>
+        <v>18.558</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.34</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6567</v>
+        <v>0.7992</v>
       </c>
       <c r="J11" t="n">
-        <v>11.8206</v>
+        <v>14.3856</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>0.86</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0727</v>
+        <v>-0.0876</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3813</v>
+        <v>-1.6644</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.62</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4485</v>
+        <v>-0.3504</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.5215</v>
+        <v>-6.6576</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.58</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5181</v>
+        <v>-0.3874</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.8439</v>
+        <v>-7.3606</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.57</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.3959</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.2942</v>
+        <v>-7.5221</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.22</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0329</v>
+        <v>-0.7296</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.6251</v>
+        <v>-13.8624</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>2.02</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9658</v>
+        <v>1.6663</v>
       </c>
       <c r="J17" t="n">
-        <v>37.3502</v>
+        <v>31.6597</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5973</v>
+        <v>1.4133</v>
       </c>
       <c r="J18" t="n">
-        <v>30.3487</v>
+        <v>26.8527</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.73</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4873</v>
+        <v>1.3464</v>
       </c>
       <c r="J19" t="n">
-        <v>28.2587</v>
+        <v>25.5816</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5206</v>
+        <v>0.6495</v>
       </c>
       <c r="J20" t="n">
-        <v>9.891400000000001</v>
+        <v>12.3405</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>1.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2213</v>
+        <v>0.3282</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2047</v>
+        <v>6.2358</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.18</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3353</v>
+        <v>0.3866</v>
       </c>
       <c r="J22" t="n">
-        <v>10.059</v>
+        <v>11.598</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3048</v>
+        <v>0.3497</v>
       </c>
       <c r="J23" t="n">
-        <v>9.144</v>
+        <v>10.491</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3048</v>
+        <v>0.3497</v>
       </c>
       <c r="J24" t="n">
-        <v>9.144</v>
+        <v>10.491</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1009</v>
+        <v>0.1313</v>
       </c>
       <c r="J25" t="n">
-        <v>3.027</v>
+        <v>3.939</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.72</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5036</v>
+        <v>-0.3231</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.108</v>
+        <v>-9.693</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.44</v>
       </c>
       <c r="I27" t="n">
-        <v>1.142</v>
+        <v>1.0845</v>
       </c>
       <c r="J27" t="n">
-        <v>34.26</v>
+        <v>32.535</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5952</v>
+        <v>0.5777</v>
       </c>
       <c r="J28" t="n">
-        <v>17.856</v>
+        <v>17.331</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5149</v>
+        <v>0.5023</v>
       </c>
       <c r="J29" t="n">
-        <v>15.447</v>
+        <v>15.069</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0888</v>
+        <v>-0.0276</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.664</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7557</v>
+        <v>-0.706</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.671</v>
+        <v>-21.18</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9538</v>
+        <v>0.6997</v>
       </c>
       <c r="J32" t="n">
-        <v>25.7526</v>
+        <v>18.8919</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.31</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8187</v>
+        <v>0.6193</v>
       </c>
       <c r="J33" t="n">
-        <v>22.1049</v>
+        <v>16.7211</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7235</v>
+        <v>0.5647</v>
       </c>
       <c r="J34" t="n">
-        <v>19.5345</v>
+        <v>15.2469</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.11</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2682</v>
+        <v>0.3289</v>
       </c>
       <c r="J35" t="n">
-        <v>7.2414</v>
+        <v>8.8803</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.91</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4464</v>
+        <v>-0.3727</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.0528</v>
+        <v>-10.0629</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4127</v>
+        <v>0.4152</v>
       </c>
       <c r="J37" t="n">
-        <v>11.1429</v>
+        <v>11.2104</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3545</v>
+        <v>0.3709</v>
       </c>
       <c r="J38" t="n">
-        <v>9.5715</v>
+        <v>10.0143</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>0.133</v>
+        <v>0.1252</v>
       </c>
       <c r="J39" t="n">
-        <v>3.591</v>
+        <v>3.3804</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3731</v>
+        <v>-0.234</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.0737</v>
+        <v>-6.318</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.676</v>
+        <v>-0.4522</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.252</v>
+        <v>-12.2094</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.63</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3946</v>
+        <v>0.9912</v>
       </c>
       <c r="J42" t="n">
-        <v>34.865</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.966</v>
+        <v>0.7362</v>
       </c>
       <c r="J43" t="n">
-        <v>24.15</v>
+        <v>18.405</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.41</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="J44" t="n">
-        <v>23.575</v>
+        <v>18.0975</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.38</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8692</v>
+        <v>0.6871</v>
       </c>
       <c r="J45" t="n">
-        <v>21.73</v>
+        <v>17.1775</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0766</v>
+        <v>0.007</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.915</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>0.91</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0664</v>
+        <v>-0.0813</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.66</v>
+        <v>-2.0325</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.8</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2499</v>
+        <v>-0.2043</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.2475</v>
+        <v>-5.1075</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4808</v>
+        <v>-0.3271</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.02</v>
+        <v>-8.1775</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4808</v>
+        <v>-0.3271</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.02</v>
+        <v>-8.1775</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6519</v>
+        <v>-0.4392</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.2975</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6482</v>
+        <v>0.4952</v>
       </c>
       <c r="J52" t="n">
-        <v>16.205</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>0.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1869</v>
+        <v>-0.1419</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.6725</v>
+        <v>-3.5475</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.72</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4601</v>
+        <v>-0.2995</v>
       </c>
       <c r="J54" t="n">
-        <v>-11.5025</v>
+        <v>-7.4875</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5158</v>
+        <v>-0.3376</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.895</v>
+        <v>-8.44</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5561</v>
+        <v>-0.366</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.9025</v>
+        <v>-9.15</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.71</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9298</v>
+        <v>0.6359</v>
       </c>
       <c r="J57" t="n">
-        <v>23.245</v>
+        <v>15.8975</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5935</v>
+        <v>0.4452</v>
       </c>
       <c r="J58" t="n">
-        <v>14.8375</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0461</v>
+        <v>0.0756</v>
       </c>
       <c r="J59" t="n">
-        <v>1.1525</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1061</v>
+        <v>-0.0406</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.6525</v>
+        <v>-1.015</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3061</v>
+        <v>-0.178</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.6525</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2872</v>
+        <v>0.9181</v>
       </c>
       <c r="J62" t="n">
-        <v>27.0312</v>
+        <v>19.2801</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>1.188</v>
+        <v>0.8565</v>
       </c>
       <c r="J63" t="n">
-        <v>24.948</v>
+        <v>17.9865</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5744</v>
+        <v>0.5253</v>
       </c>
       <c r="J64" t="n">
-        <v>12.0624</v>
+        <v>11.0313</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>1.25</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5744</v>
+        <v>0.5253</v>
       </c>
       <c r="J65" t="n">
-        <v>12.0624</v>
+        <v>11.0313</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.99</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.217</v>
+        <v>-0.1305</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.557</v>
+        <v>-2.7405</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3351</v>
+        <v>0.3498</v>
       </c>
       <c r="J67" t="n">
-        <v>7.0371</v>
+        <v>7.3458</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>0.84</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2097</v>
+        <v>-0.1717</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.4037</v>
+        <v>-3.6057</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>0.73</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.411</v>
+        <v>-0.278</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.631</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.66</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.344</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.8486</v>
+        <v>-7.224</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.51</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7161</v>
+        <v>-0.4841</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.0381</v>
+        <v>-10.1661</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2969</v>
+        <v>0.9356</v>
       </c>
       <c r="J72" t="n">
-        <v>29.8287</v>
+        <v>21.5188</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.56</v>
       </c>
       <c r="I73" t="n">
-        <v>1.2377</v>
+        <v>0.8999</v>
       </c>
       <c r="J73" t="n">
-        <v>28.4671</v>
+        <v>20.6977</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>1.2176</v>
+        <v>0.8879</v>
       </c>
       <c r="J74" t="n">
-        <v>28.0048</v>
+        <v>20.4217</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.45</v>
       </c>
       <c r="I75" t="n">
-        <v>1.005</v>
+        <v>0.7679</v>
       </c>
       <c r="J75" t="n">
-        <v>23.115</v>
+        <v>17.6617</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4157</v>
+        <v>-0.3319</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.5611</v>
+        <v>-7.6337</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>0.85</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.113</v>
+        <v>-0.118</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.599</v>
+        <v>-2.714</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>0.85</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.113</v>
+        <v>-0.118</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.599</v>
+        <v>-2.714</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.65</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4285</v>
+        <v>-0.3307</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.855499999999999</v>
+        <v>-7.6061</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.38</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.8435</v>
+        <v>-0.5812</v>
       </c>
       <c r="J80" t="n">
-        <v>-19.4005</v>
+        <v>-13.3676</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.33</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9062</v>
+        <v>-0.6291</v>
       </c>
       <c r="J81" t="n">
-        <v>-20.8426</v>
+        <v>-14.4693</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3809</v>
+        <v>1.2517</v>
       </c>
       <c r="J82" t="n">
-        <v>31.7607</v>
+        <v>28.7891</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.45</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0613</v>
+        <v>1.0541</v>
       </c>
       <c r="J83" t="n">
-        <v>24.4099</v>
+        <v>24.2443</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.34</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8121</v>
+        <v>0.8565</v>
       </c>
       <c r="J84" t="n">
-        <v>18.6783</v>
+        <v>19.6995</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2159</v>
+        <v>0.303</v>
       </c>
       <c r="J85" t="n">
-        <v>4.9657</v>
+        <v>6.969</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>1.08</v>
       </c>
       <c r="I86" t="n">
-        <v>0.132</v>
+        <v>0.2169</v>
       </c>
       <c r="J86" t="n">
-        <v>3.036</v>
+        <v>4.9887</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.16</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3793</v>
+        <v>0.4212</v>
       </c>
       <c r="J87" t="n">
-        <v>8.7239</v>
+        <v>9.6876</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.07</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2328</v>
+        <v>0.2304</v>
       </c>
       <c r="J88" t="n">
-        <v>5.3544</v>
+        <v>5.2992</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3207</v>
+        <v>-0.2111</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.3761</v>
+        <v>-4.8553</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.68</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5142</v>
+        <v>-0.3368</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.8266</v>
+        <v>-7.7464</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.4673</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.9873</v>
+        <v>-10.7479</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.57</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8589</v>
+        <v>0.8365</v>
       </c>
       <c r="J92" t="n">
-        <v>24.0492</v>
+        <v>23.422</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>0.87</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.263</v>
+        <v>-0.1616</v>
       </c>
       <c r="J93" t="n">
-        <v>-7.364</v>
+        <v>-4.5248</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2795</v>
+        <v>-0.1721</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.826</v>
+        <v>-4.8188</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4296</v>
+        <v>-0.2731</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.0288</v>
+        <v>-7.6468</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.71</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.498</v>
+        <v>-0.3214</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.944</v>
+        <v>-8.9992</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.34</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5374</v>
+        <v>0.4622</v>
       </c>
       <c r="J97" t="n">
-        <v>15.0472</v>
+        <v>12.9416</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.17</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3007</v>
+        <v>0.2542</v>
       </c>
       <c r="J98" t="n">
-        <v>8.419600000000001</v>
+        <v>7.1176</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.15</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2686</v>
+        <v>0.2283</v>
       </c>
       <c r="J99" t="n">
-        <v>7.5208</v>
+        <v>6.3924</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1039</v>
       </c>
       <c r="J100" t="n">
-        <v>2.6656</v>
+        <v>2.9092</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3909</v>
+        <v>-0.2406</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.9452</v>
+        <v>-6.7368</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1165</v>
+        <v>1.0753</v>
       </c>
       <c r="J102" t="n">
-        <v>27.9125</v>
+        <v>26.8825</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8107</v>
+        <v>0.8142</v>
       </c>
       <c r="J103" t="n">
-        <v>20.2675</v>
+        <v>20.355</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7147</v>
+        <v>0.7222</v>
       </c>
       <c r="J104" t="n">
-        <v>17.8675</v>
+        <v>18.055</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2323</v>
+        <v>0.3006</v>
       </c>
       <c r="J105" t="n">
-        <v>5.8075</v>
+        <v>7.515</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4507</v>
+        <v>-0.3762</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.2675</v>
+        <v>-9.404999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4077</v>
+        <v>0.4632</v>
       </c>
       <c r="J107" t="n">
-        <v>10.1925</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.03</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1225</v>
+        <v>0.1071</v>
       </c>
       <c r="J108" t="n">
-        <v>3.0625</v>
+        <v>2.6775</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0038</v>
+        <v>-0.0145</v>
       </c>
       <c r="J109" t="n">
-        <v>0.095</v>
+        <v>-0.3625</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.85</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2881</v>
+        <v>-0.18</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.2025</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.59</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6475</v>
+        <v>-0.431</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.1875</v>
+        <v>-10.775</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4038</v>
+        <v>0.4537</v>
       </c>
       <c r="J112" t="n">
-        <v>10.9026</v>
+        <v>12.2499</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.03</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1648</v>
+        <v>0.1428</v>
       </c>
       <c r="J113" t="n">
-        <v>4.4496</v>
+        <v>3.8556</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0603</v>
+        <v>-0.0684</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.6281</v>
+        <v>-1.8468</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.65</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5484</v>
+        <v>-0.3618</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.8068</v>
+        <v>-9.768599999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.35</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.637</v>
       </c>
       <c r="J116" t="n">
-        <v>-24.6996</v>
+        <v>-17.199</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2052</v>
+        <v>1.1415</v>
       </c>
       <c r="J117" t="n">
-        <v>32.5404</v>
+        <v>30.8205</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.49</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1444</v>
+        <v>1.1044</v>
       </c>
       <c r="J118" t="n">
-        <v>30.8988</v>
+        <v>29.8188</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9751</v>
+        <v>0.9954</v>
       </c>
       <c r="J119" t="n">
-        <v>26.3277</v>
+        <v>26.8758</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>1.29</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6708</v>
+        <v>0.7487</v>
       </c>
       <c r="J120" t="n">
-        <v>18.1116</v>
+        <v>20.2149</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5599</v>
+        <v>-0.4879</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.1173</v>
+        <v>-13.1733</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.26</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4412</v>
+        <v>0.3718</v>
       </c>
       <c r="J122" t="n">
-        <v>12.3536</v>
+        <v>10.4104</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.28</v>
+        <v>0.232</v>
       </c>
       <c r="J123" t="n">
-        <v>7.84</v>
+        <v>6.496</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2473</v>
+        <v>0.2053</v>
       </c>
       <c r="J124" t="n">
-        <v>6.9244</v>
+        <v>5.7484</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0659</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>1.8452</v>
+        <v>2.0972</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3857</v>
+        <v>-0.2377</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.7996</v>
+        <v>-6.6556</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5848</v>
+        <v>0.5402</v>
       </c>
       <c r="J127" t="n">
-        <v>16.3744</v>
+        <v>15.1256</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1958</v>
+        <v>0.1668</v>
       </c>
       <c r="J128" t="n">
-        <v>5.4824</v>
+        <v>4.6704</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.04</v>
       </c>
       <c r="I129" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>2.6264</v>
+        <v>2.3688</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2551</v>
+        <v>-0.1493</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.1428</v>
+        <v>-4.1804</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.8</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3915</v>
+        <v>-0.2431</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.962</v>
+        <v>-6.8068</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.09</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2726</v>
+        <v>0.2804</v>
       </c>
       <c r="J132" t="n">
-        <v>5.9972</v>
+        <v>6.1688</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0848</v>
+        <v>-0.0828</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.8656</v>
+        <v>-1.8216</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.89</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1584</v>
+        <v>-0.1289</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.4848</v>
+        <v>-2.8358</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.86</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2134</v>
+        <v>-0.1607</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.6948</v>
+        <v>-3.5354</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8247</v>
+        <v>-0.5662</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.1434</v>
+        <v>-12.4564</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.74</v>
       </c>
       <c r="I137" t="n">
-        <v>1.6248</v>
+        <v>1.4099</v>
       </c>
       <c r="J137" t="n">
-        <v>35.7456</v>
+        <v>31.0178</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.28</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6508</v>
+        <v>0.7276</v>
       </c>
       <c r="J138" t="n">
-        <v>14.3176</v>
+        <v>16.0072</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.21</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4764</v>
+        <v>0.5639</v>
       </c>
       <c r="J139" t="n">
-        <v>10.4808</v>
+        <v>12.4058</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>1.18</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4014</v>
+        <v>0.4897</v>
       </c>
       <c r="J140" t="n">
-        <v>8.8308</v>
+        <v>10.7734</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2988</v>
+        <v>0.3864</v>
       </c>
       <c r="J141" t="n">
-        <v>6.5736</v>
+        <v>8.5008</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.12</v>
       </c>
       <c r="I142" t="n">
-        <v>0.28</v>
+        <v>0.3012</v>
       </c>
       <c r="J142" t="n">
-        <v>7.84</v>
+        <v>8.4336</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.092</v>
+        <v>0.076</v>
       </c>
       <c r="J143" t="n">
-        <v>2.576</v>
+        <v>2.128</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0663</v>
+        <v>0.047</v>
       </c>
       <c r="J144" t="n">
-        <v>1.8564</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0047</v>
+        <v>-0.0166</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.1316</v>
+        <v>-0.4648</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6258</v>
+        <v>-0.4146</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.5224</v>
+        <v>-11.6088</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0122</v>
+        <v>1.0099</v>
       </c>
       <c r="J147" t="n">
-        <v>28.3416</v>
+        <v>28.2772</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.32</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8105</v>
+        <v>0.8266</v>
       </c>
       <c r="J148" t="n">
-        <v>22.694</v>
+        <v>23.1448</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.25</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6286</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>17.6008</v>
+        <v>18.7292</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.16</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3783</v>
+        <v>0.4525</v>
       </c>
       <c r="J150" t="n">
-        <v>10.5924</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>1.1</v>
       </c>
       <c r="I151" t="n">
-        <v>0.2146</v>
+        <v>0.2912</v>
       </c>
       <c r="J151" t="n">
-        <v>6.0088</v>
+        <v>8.153600000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3287</v>
+        <v>0.3676</v>
       </c>
       <c r="J152" t="n">
-        <v>9.861000000000001</v>
+        <v>11.028</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.01</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0477</v>
+        <v>0.0395</v>
       </c>
       <c r="J153" t="n">
-        <v>1.431</v>
+        <v>1.185</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0607</v>
+        <v>-0.0351</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.821</v>
+        <v>-1.053</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.9</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.224</v>
+        <v>-0.1329</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.72</v>
+        <v>-3.987</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.241</v>
+        <v>-0.1439</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.23</v>
+        <v>-4.317</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9187</v>
+        <v>0.9067</v>
       </c>
       <c r="J157" t="n">
-        <v>27.561</v>
+        <v>27.201</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4981</v>
       </c>
       <c r="J158" t="n">
-        <v>15.045</v>
+        <v>14.943</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4726</v>
+        <v>0.473</v>
       </c>
       <c r="J159" t="n">
-        <v>14.178</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2426</v>
+        <v>0.2887</v>
       </c>
       <c r="J160" t="n">
-        <v>7.278</v>
+        <v>8.661</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3982</v>
+        <v>-0.3279</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.946</v>
+        <v>-9.837</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8589</v>
+        <v>0.8423</v>
       </c>
       <c r="J162" t="n">
-        <v>24.0492</v>
+        <v>23.5844</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.669</v>
+        <v>0.6505</v>
       </c>
       <c r="J163" t="n">
-        <v>18.732</v>
+        <v>18.214</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6185</v>
+        <v>0.6014</v>
       </c>
       <c r="J164" t="n">
-        <v>17.318</v>
+        <v>16.8392</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2663</v>
+        <v>-0.1967</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.4564</v>
+        <v>-5.5076</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.9</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4506</v>
+        <v>-0.3832</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.6168</v>
+        <v>-10.7296</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.43</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.8325</v>
       </c>
       <c r="J167" t="n">
-        <v>18.9812</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2057</v>
+        <v>0.223</v>
       </c>
       <c r="J168" t="n">
-        <v>5.7596</v>
+        <v>6.244</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.86</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2967</v>
+        <v>-0.1788</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.307600000000001</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3274</v>
+        <v>-0.1997</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.167199999999999</v>
+        <v>-5.5916</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.84</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3274</v>
+        <v>-0.1997</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.167199999999999</v>
+        <v>-5.5916</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.64</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4197</v>
+        <v>1.2796</v>
       </c>
       <c r="J172" t="n">
-        <v>32.6531</v>
+        <v>29.4308</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.36</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8277</v>
+        <v>0.8934</v>
       </c>
       <c r="J173" t="n">
-        <v>19.0371</v>
+        <v>20.5482</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.29</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6469</v>
+        <v>0.7415</v>
       </c>
       <c r="J174" t="n">
-        <v>14.8787</v>
+        <v>17.0545</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.28</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6231</v>
+        <v>0.7188</v>
       </c>
       <c r="J175" t="n">
-        <v>14.3313</v>
+        <v>16.5324</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>1.22</v>
       </c>
       <c r="I176" t="n">
-        <v>0.4801</v>
+        <v>0.5779</v>
       </c>
       <c r="J176" t="n">
-        <v>11.0423</v>
+        <v>13.2917</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.04</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2136</v>
+        <v>0.201</v>
       </c>
       <c r="J177" t="n">
-        <v>4.9128</v>
+        <v>4.623</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.91</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0859</v>
+        <v>-0.0917</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.9757</v>
+        <v>-2.1091</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.76</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3514</v>
+        <v>-0.2493</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.0822</v>
+        <v>-5.7339</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.67</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4992</v>
+        <v>-0.3334</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.4816</v>
+        <v>-7.6682</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.43</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8127</v>
+        <v>-0.5568</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.6921</v>
+        <v>-12.8064</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.36</v>
       </c>
       <c r="I182" t="n">
-        <v>0.538</v>
+        <v>0.4701</v>
       </c>
       <c r="J182" t="n">
-        <v>14.526</v>
+        <v>12.6927</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.3</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4598</v>
+        <v>0.4011</v>
       </c>
       <c r="J183" t="n">
-        <v>12.4146</v>
+        <v>10.8297</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2738</v>
+        <v>0.2588</v>
       </c>
       <c r="J184" t="n">
-        <v>7.3926</v>
+        <v>6.9876</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.15</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2225</v>
+        <v>0.2212</v>
       </c>
       <c r="J185" t="n">
-        <v>6.0075</v>
+        <v>5.9724</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2042</v>
+        <v>-0.1074</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.5134</v>
+        <v>-2.8998</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8747</v>
+        <v>0.8532</v>
       </c>
       <c r="J187" t="n">
-        <v>23.6169</v>
+        <v>23.0364</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3934</v>
+        <v>0.3429</v>
       </c>
       <c r="J188" t="n">
-        <v>10.6218</v>
+        <v>9.2583</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.85</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3011</v>
+        <v>-0.1847</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.1297</v>
+        <v>-4.9869</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.77</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4198</v>
+        <v>-0.2655</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.3346</v>
+        <v>-7.1685</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.45</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8176</v>
+        <v>-0.5613</v>
       </c>
       <c r="J191" t="n">
-        <v>-22.0752</v>
+        <v>-15.1551</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.31</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>14.755</v>
+        <v>17.805</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.89</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1605</v>
+        <v>-0.1294</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.0125</v>
+        <v>-3.235</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.8</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3335</v>
+        <v>-0.22</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.3375</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5392</v>
+        <v>-0.3546</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.48</v>
+        <v>-8.865</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6688</v>
+        <v>-0.4479</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.72</v>
+        <v>-11.1975</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0547</v>
+        <v>1.04</v>
       </c>
       <c r="J197" t="n">
-        <v>26.3675</v>
+        <v>26</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.23</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5647</v>
+        <v>0.6236</v>
       </c>
       <c r="J198" t="n">
-        <v>14.1175</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.22</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5373</v>
+        <v>0.6002</v>
       </c>
       <c r="J199" t="n">
-        <v>13.4325</v>
+        <v>15.005</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.2</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4839</v>
+        <v>0.5523</v>
       </c>
       <c r="J200" t="n">
-        <v>12.0975</v>
+        <v>13.8075</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>1.16</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3783</v>
+        <v>0.4525</v>
       </c>
       <c r="J201" t="n">
-        <v>9.4575</v>
+        <v>11.3125</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.51</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7883</v>
+        <v>0.9817</v>
       </c>
       <c r="J202" t="n">
-        <v>26.8022</v>
+        <v>33.3778</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.96</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0921</v>
+        <v>-0.0601</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.1314</v>
+        <v>-2.0434</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.92</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.178</v>
+        <v>-0.1077</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.052</v>
+        <v>-3.6618</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4032</v>
+        <v>-0.2544</v>
       </c>
       <c r="J205" t="n">
-        <v>-13.7088</v>
+        <v>-8.6496</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5904</v>
+        <v>-0.3882</v>
       </c>
       <c r="J206" t="n">
-        <v>-20.0736</v>
+        <v>-13.1988</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6069</v>
+        <v>1.3953</v>
       </c>
       <c r="J207" t="n">
-        <v>54.6346</v>
+        <v>47.4402</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.37</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0114</v>
+        <v>0.9883</v>
       </c>
       <c r="J208" t="n">
-        <v>34.3876</v>
+        <v>33.6022</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.85</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.5726</v>
+        <v>-0.5134</v>
       </c>
       <c r="J209" t="n">
-        <v>-19.4684</v>
+        <v>-17.4556</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.7464</v>
+        <v>-0.6975</v>
       </c>
       <c r="J210" t="n">
-        <v>-25.3776</v>
+        <v>-23.715</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.76</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7935</v>
+        <v>-0.7484</v>
       </c>
       <c r="J211" t="n">
-        <v>-26.979</v>
+        <v>-25.4456</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.23</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4282</v>
+        <v>0.379</v>
       </c>
       <c r="J212" t="n">
-        <v>12.4178</v>
+        <v>10.991</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.22</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4142</v>
+        <v>0.3652</v>
       </c>
       <c r="J213" t="n">
-        <v>12.0118</v>
+        <v>10.5908</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1906</v>
+        <v>-0.111</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.5274</v>
+        <v>-3.219</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3074</v>
+        <v>-0.1873</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.9146</v>
+        <v>-5.4317</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4524</v>
+        <v>-0.2876</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.1196</v>
+        <v>-8.340400000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5322</v>
+        <v>0.4556</v>
       </c>
       <c r="J217" t="n">
-        <v>15.4338</v>
+        <v>13.2124</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2785</v>
+        <v>0.2315</v>
       </c>
       <c r="J218" t="n">
-        <v>8.076499999999999</v>
+        <v>6.7135</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1263</v>
+        <v>0.1216</v>
       </c>
       <c r="J219" t="n">
-        <v>3.6627</v>
+        <v>3.5264</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0747</v>
+        <v>-0.0281</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.1663</v>
+        <v>-0.8149</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2979</v>
+        <v>-0.176</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.639099999999999</v>
+        <v>-5.104</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.19</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5642</v>
       </c>
       <c r="J222" t="n">
-        <v>17.2028</v>
+        <v>16.3618</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5135</v>
+        <v>0.487</v>
       </c>
       <c r="J223" t="n">
-        <v>14.8915</v>
+        <v>14.123</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3991</v>
+        <v>0.3809</v>
       </c>
       <c r="J224" t="n">
-        <v>11.5739</v>
+        <v>11.0461</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2111</v>
+        <v>-0.1506</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.1219</v>
+        <v>-4.3674</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2472</v>
+        <v>-0.1855</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.1688</v>
+        <v>-5.3795</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.16</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3179</v>
+        <v>0.3589</v>
       </c>
       <c r="J227" t="n">
-        <v>9.219099999999999</v>
+        <v>10.4081</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2545</v>
+        <v>0.282</v>
       </c>
       <c r="J228" t="n">
-        <v>7.3805</v>
+        <v>8.178000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2033</v>
+        <v>0.2217</v>
       </c>
       <c r="J229" t="n">
-        <v>5.8957</v>
+        <v>6.4293</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1219</v>
+        <v>-0.065</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.5351</v>
+        <v>-1.885</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.76</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4436</v>
+        <v>-0.2806</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.8644</v>
+        <v>-8.1374</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0998</v>
+        <v>1.064</v>
       </c>
       <c r="J232" t="n">
-        <v>27.495</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.34</v>
       </c>
       <c r="I233" t="n">
-        <v>0.884</v>
+        <v>0.8849</v>
       </c>
       <c r="J233" t="n">
-        <v>22.1</v>
+        <v>22.1225</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.13</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3218</v>
+        <v>0.3847</v>
       </c>
       <c r="J234" t="n">
-        <v>8.045</v>
+        <v>9.6175</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.09</v>
       </c>
       <c r="I235" t="n">
-        <v>0.207</v>
+        <v>0.274</v>
       </c>
       <c r="J235" t="n">
-        <v>5.175</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1233</v>
+        <v>-0.0486</v>
       </c>
       <c r="J236" t="n">
-        <v>-3.0825</v>
+        <v>-1.215</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.34</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5895</v>
+        <v>0.709</v>
       </c>
       <c r="J237" t="n">
-        <v>14.7375</v>
+        <v>17.725</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.09</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2307</v>
+        <v>0.2399</v>
       </c>
       <c r="J238" t="n">
-        <v>5.7675</v>
+        <v>5.9975</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2089</v>
+        <v>-0.1286</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.2225</v>
+        <v>-3.215</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.414</v>
+        <v>-0.2626</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.35</v>
+        <v>-6.565</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5879</v>
+        <v>-0.3866</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.6975</v>
+        <v>-9.664999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4187</v>
+        <v>0.4745</v>
       </c>
       <c r="J242" t="n">
-        <v>9.630100000000001</v>
+        <v>10.9135</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>0.84</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2213</v>
+        <v>-0.1752</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.0899</v>
+        <v>-4.0296</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.73</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4215</v>
+        <v>-0.2809</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.6945</v>
+        <v>-6.4607</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.61</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5923</v>
+        <v>-0.3942</v>
       </c>
       <c r="J245" t="n">
-        <v>-13.6229</v>
+        <v>-9.066599999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.61</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5923</v>
+        <v>-0.3942</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.6229</v>
+        <v>-9.066599999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3655</v>
+        <v>1.2412</v>
       </c>
       <c r="J247" t="n">
-        <v>31.4065</v>
+        <v>28.5476</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.47</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1072</v>
+        <v>1.0808</v>
       </c>
       <c r="J248" t="n">
-        <v>25.4656</v>
+        <v>24.8584</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>1.41</v>
       </c>
       <c r="I249" t="n">
-        <v>0.9794</v>
+        <v>0.9969</v>
       </c>
       <c r="J249" t="n">
-        <v>22.5262</v>
+        <v>22.9287</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>1.29</v>
       </c>
       <c r="I250" t="n">
-        <v>0.6767</v>
+        <v>0.7499</v>
       </c>
       <c r="J250" t="n">
-        <v>15.5641</v>
+        <v>17.2477</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7998</v>
+        <v>-0.7504</v>
       </c>
       <c r="J251" t="n">
-        <v>-18.3954</v>
+        <v>-17.2592</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.7</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9603</v>
+        <v>1.1381</v>
       </c>
       <c r="J252" t="n">
-        <v>28.809</v>
+        <v>34.143</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1124</v>
+        <v>0.1511</v>
       </c>
       <c r="J253" t="n">
-        <v>3.372</v>
+        <v>4.533</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1777</v>
+        <v>-0.0955</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.331</v>
+        <v>-2.865</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1777</v>
+        <v>-0.0955</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.331</v>
+        <v>-2.865</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5191</v>
+        <v>-0.3343</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.573</v>
+        <v>-10.029</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4874</v>
+        <v>0.4479</v>
       </c>
       <c r="J257" t="n">
-        <v>14.622</v>
+        <v>13.437</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.08</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3087</v>
+        <v>0.2795</v>
       </c>
       <c r="J258" t="n">
-        <v>9.260999999999999</v>
+        <v>8.385</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.04</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1633</v>
+        <v>0.1565</v>
       </c>
       <c r="J259" t="n">
-        <v>4.899</v>
+        <v>4.695</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>1.02</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0693</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J260" t="n">
-        <v>2.079</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.9</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.415</v>
+        <v>-0.3592</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.45</v>
+        <v>-10.776</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.21</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4256</v>
+        <v>0.4862</v>
       </c>
       <c r="J262" t="n">
-        <v>12.768</v>
+        <v>14.586</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>0.97</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0409</v>
+        <v>-0.0434</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.227</v>
+        <v>-1.302</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.896</v>
+        <v>-1.704</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1061</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.183</v>
+        <v>-2.448</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7187</v>
+        <v>-0.4847</v>
       </c>
       <c r="J266" t="n">
-        <v>-21.561</v>
+        <v>-14.541</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.5</v>
       </c>
       <c r="I267" t="n">
-        <v>1.2282</v>
+        <v>1.1444</v>
       </c>
       <c r="J267" t="n">
-        <v>36.846</v>
+        <v>34.332</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.18</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4741</v>
+        <v>0.5143</v>
       </c>
       <c r="J268" t="n">
-        <v>14.223</v>
+        <v>15.429</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>1.16</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4145</v>
+        <v>0.4649</v>
       </c>
       <c r="J269" t="n">
-        <v>12.435</v>
+        <v>13.947</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>1.15</v>
       </c>
       <c r="I270" t="n">
-        <v>0.3858</v>
+        <v>0.4395</v>
       </c>
       <c r="J270" t="n">
-        <v>11.574</v>
+        <v>13.185</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.95</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3245</v>
+        <v>-0.2474</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.734999999999999</v>
+        <v>-7.422</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.47</v>
       </c>
       <c r="I272" t="n">
-        <v>0.799</v>
+        <v>1.006</v>
       </c>
       <c r="J272" t="n">
-        <v>19.975</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>0.75</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.4009</v>
+        <v>-0.265</v>
       </c>
       <c r="J273" t="n">
-        <v>-10.0225</v>
+        <v>-6.625</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>0.7</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.4753</v>
+        <v>-0.3128</v>
       </c>
       <c r="J274" t="n">
-        <v>-11.8825</v>
+        <v>-7.82</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5986</v>
+        <v>-0.3977</v>
       </c>
       <c r="J275" t="n">
-        <v>-14.965</v>
+        <v>-9.942500000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.55</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6756</v>
+        <v>-0.4534</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.89</v>
+        <v>-11.335</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.79</v>
       </c>
       <c r="I277" t="n">
-        <v>1.692</v>
+        <v>1.4566</v>
       </c>
       <c r="J277" t="n">
-        <v>42.3</v>
+        <v>36.415</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>1.56</v>
       </c>
       <c r="I278" t="n">
-        <v>1.2649</v>
+        <v>1.1829</v>
       </c>
       <c r="J278" t="n">
-        <v>31.6225</v>
+        <v>29.5725</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>1.17</v>
       </c>
       <c r="I279" t="n">
-        <v>0.357</v>
+        <v>0.4533</v>
       </c>
       <c r="J279" t="n">
-        <v>8.925000000000001</v>
+        <v>11.3325</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>1.16</v>
       </c>
       <c r="I280" t="n">
-        <v>0.332</v>
+        <v>0.4276</v>
       </c>
       <c r="J280" t="n">
-        <v>8.300000000000001</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>1.12</v>
       </c>
       <c r="I281" t="n">
-        <v>0.2289</v>
+        <v>0.3212</v>
       </c>
       <c r="J281" t="n">
-        <v>5.7225</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.15</v>
       </c>
       <c r="I282" t="n">
-        <v>0.399</v>
+        <v>0.4482</v>
       </c>
       <c r="J282" t="n">
-        <v>8.778</v>
+        <v>9.8604</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.86</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.175</v>
+        <v>-0.15</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.85</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.78</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3126</v>
+        <v>-0.2315</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.8772</v>
+        <v>-5.093</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.57</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6388</v>
+        <v>-0.428</v>
       </c>
       <c r="J285" t="n">
-        <v>-14.0536</v>
+        <v>-9.416</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.48</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7529</v>
+        <v>-0.5115</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.5638</v>
+        <v>-11.253</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.55</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2339</v>
+        <v>1.1668</v>
       </c>
       <c r="J287" t="n">
-        <v>27.1458</v>
+        <v>25.6696</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.53</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1937</v>
+        <v>1.1427</v>
       </c>
       <c r="J288" t="n">
-        <v>26.2614</v>
+        <v>25.1394</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.43</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9813</v>
+        <v>1.0165</v>
       </c>
       <c r="J289" t="n">
-        <v>21.5886</v>
+        <v>22.363</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.21</v>
       </c>
       <c r="I290" t="n">
-        <v>0.4461</v>
+        <v>0.5481</v>
       </c>
       <c r="J290" t="n">
-        <v>9.8142</v>
+        <v>12.0582</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>1.2</v>
       </c>
       <c r="I291" t="n">
-        <v>0.4221</v>
+        <v>0.5235</v>
       </c>
       <c r="J291" t="n">
-        <v>9.286199999999999</v>
+        <v>11.517</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.39</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6363</v>
+        <v>0.7745</v>
       </c>
       <c r="J292" t="n">
-        <v>15.9075</v>
+        <v>19.3625</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.03</v>
       </c>
       <c r="I293" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>2.405</v>
+        <v>2.3325</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.99</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.034</v>
+        <v>-0.0201</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.85</v>
+        <v>-0.5024999999999999</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.82</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3524</v>
+        <v>-0.2179</v>
       </c>
       <c r="J295" t="n">
-        <v>-8.81</v>
+        <v>-5.4475</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4791</v>
+        <v>-0.3067</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.9775</v>
+        <v>-7.6675</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.59</v>
       </c>
       <c r="I297" t="n">
-        <v>1.4405</v>
+        <v>1.2815</v>
       </c>
       <c r="J297" t="n">
-        <v>36.0125</v>
+        <v>32.0375</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.16</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4884</v>
+        <v>0.4773</v>
       </c>
       <c r="J298" t="n">
-        <v>12.21</v>
+        <v>11.9325</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3989</v>
+        <v>0.3999</v>
       </c>
       <c r="J299" t="n">
-        <v>9.9725</v>
+        <v>9.9975</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.06</v>
       </c>
       <c r="I300" t="n">
-        <v>0.159</v>
+        <v>0.2044</v>
       </c>
       <c r="J300" t="n">
-        <v>3.975</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.066</v>
+        <v>-1.0494</v>
       </c>
       <c r="J301" t="n">
-        <v>-26.65</v>
+        <v>-26.235</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>2.38</v>
       </c>
       <c r="I302" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J302" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.78</v>
       </c>
       <c r="I303" t="n">
-        <v>1.515</v>
+        <v>1.3863</v>
       </c>
       <c r="J303" t="n">
-        <v>25.755</v>
+        <v>23.5671</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.62</v>
       </c>
       <c r="I304" t="n">
-        <v>1.1817</v>
+        <v>1.2123</v>
       </c>
       <c r="J304" t="n">
-        <v>20.0889</v>
+        <v>20.6091</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.51</v>
       </c>
       <c r="I305" t="n">
-        <v>0.9705</v>
+        <v>1.0841</v>
       </c>
       <c r="J305" t="n">
-        <v>16.4985</v>
+        <v>18.4297</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.38</v>
       </c>
       <c r="I306" t="n">
-        <v>0.7154</v>
+        <v>0.87</v>
       </c>
       <c r="J306" t="n">
-        <v>12.1618</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>0.92</v>
       </c>
       <c r="I307" t="n">
-        <v>0.0774</v>
+        <v>0.0673</v>
       </c>
       <c r="J307" t="n">
-        <v>1.3158</v>
+        <v>1.1441</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.42</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.7479</v>
+        <v>-0.5194</v>
       </c>
       <c r="J308" t="n">
-        <v>-12.7143</v>
+        <v>-8.829800000000001</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.4</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.5387</v>
       </c>
       <c r="J309" t="n">
-        <v>-13.2209</v>
+        <v>-9.1579</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.4</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.5387</v>
       </c>
       <c r="J310" t="n">
-        <v>-13.2209</v>
+        <v>-9.1579</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.35</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.8491</v>
+        <v>-0.5879</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.4347</v>
+        <v>-9.994300000000001</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.8</v>
       </c>
       <c r="I312" t="n">
-        <v>1.6818</v>
+        <v>1.4533</v>
       </c>
       <c r="J312" t="n">
-        <v>36.9996</v>
+        <v>31.9726</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.62</v>
       </c>
       <c r="I313" t="n">
-        <v>1.3514</v>
+        <v>1.2436</v>
       </c>
       <c r="J313" t="n">
-        <v>29.7308</v>
+        <v>27.3592</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.44</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.0262</v>
       </c>
       <c r="J314" t="n">
-        <v>21.4566</v>
+        <v>22.5764</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.27</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5707</v>
+        <v>0.6821</v>
       </c>
       <c r="J315" t="n">
-        <v>12.5554</v>
+        <v>15.0062</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>1</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1876</v>
+        <v>-0.1003</v>
       </c>
       <c r="J316" t="n">
-        <v>-4.1272</v>
+        <v>-2.2066</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>0.97</v>
       </c>
       <c r="I317" t="n">
-        <v>0.0561</v>
+        <v>0.0071</v>
       </c>
       <c r="J317" t="n">
-        <v>1.2342</v>
+        <v>0.1562</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>0.75</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.3226</v>
+        <v>-0.2515</v>
       </c>
       <c r="J318" t="n">
-        <v>-7.0972</v>
+        <v>-5.533</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.64</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.5192</v>
+        <v>-0.3526</v>
       </c>
       <c r="J319" t="n">
-        <v>-11.4224</v>
+        <v>-7.7572</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.59</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5919</v>
+        <v>-0.3992</v>
       </c>
       <c r="J320" t="n">
-        <v>-13.0218</v>
+        <v>-8.782400000000001</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.57</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6197</v>
+        <v>-0.4179</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.6334</v>
+        <v>-9.1938</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4574/event_4574_evp_summary.xlsx
+++ b/database/event/4574/event_4574_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.830500000000001</v>
+        <v>9.028</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0537</v>
+        <v>3.122</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3485</v>
+        <v>3.4855</v>
       </c>
       <c r="E2" t="n">
-        <v>8.830500000000001</v>
+        <v>9.028</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6087</v>
+        <v>3.5329</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2219</v>
+        <v>5.4951</v>
       </c>
       <c r="H2" t="n">
-        <v>7.2283</v>
+        <v>6.7623</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7584</v>
+        <v>3.6516</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2219</v>
+        <v>5.4951</v>
       </c>
       <c r="K2" t="n">
         <v>122</v>
@@ -529,7 +529,7 @@
         <v>119</v>
       </c>
       <c r="M2" t="n">
-        <v>8.9803</v>
+        <v>9.146699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>241</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4747</v>
+        <v>7.6707</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5848</v>
+        <v>2.6526</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7364</v>
+        <v>2.8677</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4747</v>
+        <v>7.6707</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4359</v>
+        <v>3.3753</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0388</v>
+        <v>4.2954</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6196</v>
+        <v>6.2423</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4419</v>
+        <v>3.3708</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0388</v>
+        <v>4.2954</v>
       </c>
       <c r="K3" t="n">
         <v>122</v>
@@ -575,7 +575,7 @@
         <v>119</v>
       </c>
       <c r="M3" t="n">
-        <v>7.480700000000001</v>
+        <v>7.6662</v>
       </c>
       <c r="N3" t="n">
         <v>241</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.2714</v>
+        <v>7.5164</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5145</v>
+        <v>2.5993</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6447</v>
+        <v>2.7974</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2714</v>
+        <v>7.5164</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9012</v>
+        <v>2.9068</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3702</v>
+        <v>4.6096</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7358</v>
+        <v>4.6964</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4624</v>
+        <v>2.536</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3702</v>
+        <v>4.6096</v>
       </c>
       <c r="K4" t="n">
         <v>122</v>
@@ -621,7 +621,7 @@
         <v>119</v>
       </c>
       <c r="M4" t="n">
-        <v>6.832599999999999</v>
+        <v>7.1456</v>
       </c>
       <c r="N4" t="n">
         <v>241</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1707</v>
+        <v>5.5503</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7881</v>
+        <v>1.9194</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6963</v>
+        <v>1.9024</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1707</v>
+        <v>5.5503</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6628</v>
+        <v>1.6572</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5079</v>
+        <v>3.8931</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6628</v>
+        <v>1.6572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8646</v>
+        <v>0.8949</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5079</v>
+        <v>3.8931</v>
       </c>
       <c r="K5" t="n">
         <v>122</v>
@@ -667,7 +667,7 @@
         <v>119</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3725</v>
+        <v>4.788</v>
       </c>
       <c r="N5" t="n">
         <v>241</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7385</v>
+        <v>4.6561</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6386</v>
+        <v>1.6101</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5012</v>
+        <v>1.4953</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7385</v>
+        <v>4.6561</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0615</v>
+        <v>3.955</v>
       </c>
       <c r="G6" t="n">
-        <v>0.677</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>8.824</v>
+        <v>8.1548</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5881</v>
+        <v>4.4035</v>
       </c>
       <c r="J6" t="n">
-        <v>0.677</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>210</v>
@@ -713,7 +713,7 @@
         <v>69</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2651</v>
+        <v>5.1046</v>
       </c>
       <c r="N6" t="n">
         <v>279</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4855</v>
+        <v>4.5007</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5511</v>
+        <v>1.5564</v>
       </c>
       <c r="D7" t="n">
-        <v>1.387</v>
+        <v>1.4246</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4855</v>
+        <v>4.5007</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7282</v>
+        <v>3.6549</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7573</v>
+        <v>0.8458</v>
       </c>
       <c r="H7" t="n">
-        <v>7.6495</v>
+        <v>7.1647</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9774</v>
+        <v>3.8689</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7573</v>
+        <v>0.8458</v>
       </c>
       <c r="K7" t="n">
         <v>122</v>
@@ -759,7 +759,7 @@
         <v>119</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7347</v>
+        <v>4.7147</v>
       </c>
       <c r="N7" t="n">
         <v>241</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2834</v>
+        <v>4.1885</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4813</v>
+        <v>1.4484</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2957</v>
+        <v>1.2825</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2834</v>
+        <v>4.1885</v>
       </c>
       <c r="F8" t="n">
-        <v>3.9495</v>
+        <v>3.8368</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3339</v>
+        <v>0.3517</v>
       </c>
       <c r="H8" t="n">
-        <v>8.429399999999999</v>
+        <v>7.7649</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3829</v>
+        <v>4.193</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3339</v>
+        <v>0.3517</v>
       </c>
       <c r="K8" t="n">
         <v>182</v>
@@ -805,7 +805,7 @@
         <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7168</v>
+        <v>4.5447</v>
       </c>
       <c r="N8" t="n">
         <v>234</v>
@@ -814,81 +814,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1476</v>
+        <v>4.1883</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4343</v>
+        <v>1.4484</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2344</v>
+        <v>1.2824</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1476</v>
+        <v>4.1883</v>
       </c>
       <c r="F9" t="n">
-        <v>3.981</v>
+        <v>2.6313</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1666</v>
+        <v>1.557</v>
       </c>
       <c r="H9" t="n">
-        <v>8.5404</v>
+        <v>3.7875</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4406</v>
+        <v>2.0452</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1666</v>
+        <v>1.557</v>
       </c>
       <c r="K9" t="n">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6072</v>
+        <v>3.6022</v>
       </c>
       <c r="N9" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1303</v>
+        <v>4.0272</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4283</v>
+        <v>1.3927</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2266</v>
+        <v>1.2091</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1303</v>
+        <v>4.0272</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7056</v>
+        <v>2.5751</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4247</v>
+        <v>1.4522</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0465</v>
+        <v>3.6019</v>
       </c>
       <c r="I10" t="n">
-        <v>2.104</v>
+        <v>1.945</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4247</v>
+        <v>1.4522</v>
       </c>
       <c r="K10" t="n">
         <v>111</v>
@@ -897,7 +897,7 @@
         <v>136</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5287</v>
+        <v>3.3972</v>
       </c>
       <c r="N10" t="n">
         <v>247</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0378</v>
+        <v>4.0185</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3963</v>
+        <v>1.3896</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1849</v>
+        <v>1.2051</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0378</v>
+        <v>4.0185</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0106</v>
+        <v>3.8524</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0272</v>
+        <v>0.1661</v>
       </c>
       <c r="H11" t="n">
-        <v>8.644600000000001</v>
+        <v>7.8162</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4948</v>
+        <v>4.2207</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0272</v>
+        <v>0.1661</v>
       </c>
       <c r="K11" t="n">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="L11" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="M11" t="n">
-        <v>4.521999999999999</v>
+        <v>4.3868</v>
       </c>
       <c r="N11" t="n">
-        <v>279</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.9229</v>
+        <v>4.0082</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3566</v>
+        <v>1.3861</v>
       </c>
       <c r="D12" t="n">
-        <v>1.133</v>
+        <v>1.2004</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9229</v>
+        <v>4.0082</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6474</v>
+        <v>3.9282</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2755</v>
+        <v>0.08</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8413</v>
+        <v>8.0664</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9973</v>
+        <v>4.3558</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2755</v>
+        <v>0.08</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="L12" t="n">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2728</v>
+        <v>4.4358</v>
       </c>
       <c r="N12" t="n">
-        <v>247</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1723</v>
+        <v>3.2109</v>
       </c>
       <c r="C13" t="n">
-        <v>1.097</v>
+        <v>1.1104</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7941</v>
+        <v>0.8375</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1723</v>
+        <v>3.2109</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4913</v>
+        <v>2.4048</v>
       </c>
       <c r="G13" t="n">
-        <v>0.681</v>
+        <v>0.8061</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2914</v>
+        <v>3.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7114</v>
+        <v>1.6416</v>
       </c>
       <c r="J13" t="n">
-        <v>0.681</v>
+        <v>0.8061</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1035,7 +1035,7 @@
         <v>136</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3924</v>
+        <v>2.4477</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6545</v>
+        <v>2.4415</v>
       </c>
       <c r="C14" t="n">
-        <v>0.918</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5604</v>
+        <v>0.4872</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6545</v>
+        <v>2.4415</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6545</v>
+        <v>2.4415</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6545</v>
+        <v>2.6187</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6545</v>
+        <v>2.6187</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6545</v>
+        <v>2.6187</v>
       </c>
       <c r="N14" t="n">
         <v>207</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4568</v>
+        <v>2.4266</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8496</v>
+        <v>0.8391</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4711</v>
+        <v>0.4804</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4568</v>
+        <v>2.4266</v>
       </c>
       <c r="F15" t="n">
-        <v>2.252</v>
+        <v>2.1795</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2048</v>
+        <v>0.2471</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4485</v>
+        <v>2.2969</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2731</v>
+        <v>1.2403</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2048</v>
+        <v>0.2471</v>
       </c>
       <c r="K15" t="n">
         <v>111</v>
@@ -1127,7 +1127,7 @@
         <v>136</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4779</v>
+        <v>1.4874</v>
       </c>
       <c r="N15" t="n">
         <v>247</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1974</v>
+        <v>2.1685</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7599</v>
+        <v>0.7499</v>
       </c>
       <c r="D16" t="n">
-        <v>0.354</v>
+        <v>0.3629</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1974</v>
+        <v>2.1685</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1974</v>
+        <v>2.1685</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1974</v>
+        <v>2.1685</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1974</v>
+        <v>2.1685</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1974</v>
+        <v>2.1685</v>
       </c>
       <c r="N16" t="n">
         <v>189</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1871</v>
+        <v>2.1077</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7563</v>
+        <v>0.7289</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3494</v>
+        <v>0.3353</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1871</v>
+        <v>2.1077</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1871</v>
+        <v>2.1077</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1871</v>
+        <v>2.1077</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1871</v>
+        <v>2.1077</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1871</v>
+        <v>2.1077</v>
       </c>
       <c r="N17" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1213</v>
+        <v>2.0733</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7336</v>
+        <v>0.717</v>
       </c>
       <c r="D18" t="n">
         <v>0.3196</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1213</v>
+        <v>2.0733</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1213</v>
+        <v>2.0733</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1213</v>
+        <v>2.0733</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1213</v>
+        <v>2.0733</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1213</v>
+        <v>2.0733</v>
       </c>
       <c r="N18" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0871</v>
+        <v>1.938</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7217</v>
+        <v>0.6702</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3042</v>
+        <v>0.258</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0871</v>
+        <v>1.938</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4174</v>
+        <v>2.3173</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3303</v>
+        <v>-0.3793</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0312</v>
+        <v>2.7515</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5761</v>
+        <v>1.4858</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3303</v>
+        <v>-0.3793</v>
       </c>
       <c r="K19" t="n">
         <v>210</v>
@@ -1311,7 +1311,7 @@
         <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2458</v>
+        <v>1.1065</v>
       </c>
       <c r="N19" t="n">
         <v>279</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.071</v>
+        <v>1.9355</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6693</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2969</v>
+        <v>0.2569</v>
       </c>
       <c r="E20" t="n">
-        <v>2.071</v>
+        <v>1.9355</v>
       </c>
       <c r="F20" t="n">
-        <v>2.385</v>
+        <v>2.2569</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.314</v>
+        <v>-0.3214</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9168</v>
+        <v>2.5523</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5166</v>
+        <v>1.3782</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.314</v>
+        <v>-0.3214</v>
       </c>
       <c r="K20" t="n">
         <v>182</v>
@@ -1357,7 +1357,7 @@
         <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2026</v>
+        <v>1.0568</v>
       </c>
       <c r="N20" t="n">
         <v>234</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9378</v>
+        <v>1.8979</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6701</v>
+        <v>0.6563</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2368</v>
+        <v>0.2398</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9378</v>
+        <v>1.8979</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9378</v>
+        <v>1.8979</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9378</v>
+        <v>1.8979</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9378</v>
+        <v>1.8979</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9378</v>
+        <v>1.8979</v>
       </c>
       <c r="N21" t="n">
         <v>189</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7614</v>
+        <v>1.7225</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6091</v>
+        <v>0.5957</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1572</v>
+        <v>0.1599</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7614</v>
+        <v>1.7225</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7614</v>
+        <v>1.7225</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7614</v>
+        <v>1.7225</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7614</v>
+        <v>1.7225</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7614</v>
+        <v>1.7225</v>
       </c>
       <c r="N22" t="n">
         <v>207</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6502</v>
+        <v>1.5195</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5707</v>
+        <v>0.5255</v>
       </c>
       <c r="D23" t="n">
-        <v>0.107</v>
+        <v>0.0675</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6502</v>
+        <v>1.5195</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4295</v>
+        <v>2.3251</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7793</v>
+        <v>-0.8056</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0737</v>
+        <v>2.7773</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5982</v>
+        <v>1.4997</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7793</v>
+        <v>-0.8056</v>
       </c>
       <c r="K23" t="n">
         <v>182</v>
@@ -1495,7 +1495,7 @@
         <v>52</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8189000000000001</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>234</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4635</v>
+        <v>1.4556</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5061</v>
+        <v>0.5034</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0227</v>
+        <v>0.0384</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4635</v>
+        <v>1.4556</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3131</v>
+        <v>2.5518</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8496</v>
+        <v>-1.0962</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6635</v>
+        <v>3.5251</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3849</v>
+        <v>1.9035</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8496</v>
+        <v>-1.0962</v>
       </c>
       <c r="K24" t="n">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="L24" t="n">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5353</v>
+        <v>0.8072999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>279</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4394</v>
+        <v>1.3602</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4978</v>
+        <v>0.4704</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0118</v>
+        <v>-0.005</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4394</v>
+        <v>1.3602</v>
       </c>
       <c r="F25" t="n">
-        <v>2.612</v>
+        <v>2.2162</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1726</v>
+        <v>-0.856</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7167</v>
+        <v>2.4178</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9325</v>
+        <v>1.3056</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.1726</v>
+        <v>-0.856</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="L25" t="n">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7599</v>
+        <v>0.4496000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>247</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.0795</v>
+        <v>0.998</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3733</v>
+        <v>0.3451</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1507</v>
+        <v>-0.1699</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0795</v>
+        <v>0.998</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0795</v>
+        <v>0.998</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0795</v>
+        <v>0.998</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0795</v>
+        <v>0.998</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0795</v>
+        <v>0.998</v>
       </c>
       <c r="N26" t="n">
         <v>104</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7421</v>
+        <v>0.7315</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2566</v>
+        <v>0.253</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.303</v>
+        <v>-0.2912</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7421</v>
+        <v>0.7315</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7421</v>
+        <v>0.7315</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7421</v>
+        <v>0.7315</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7421</v>
+        <v>0.7315</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7421</v>
+        <v>0.7315</v>
       </c>
       <c r="N27" t="n">
         <v>189</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3125</v>
+        <v>0.2244</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1081</v>
+        <v>0.0776</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4969</v>
+        <v>-0.5221</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3125</v>
+        <v>0.2244</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3125</v>
+        <v>0.2244</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3125</v>
+        <v>0.2244</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3125</v>
+        <v>0.2244</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3125</v>
+        <v>0.2244</v>
       </c>
       <c r="N28" t="n">
         <v>104</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1362</v>
+        <v>0.0536</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0471</v>
+        <v>0.0185</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5765</v>
+        <v>-0.5998</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1362</v>
+        <v>0.0536</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1362</v>
+        <v>0.0536</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1362</v>
+        <v>0.0536</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1362</v>
+        <v>0.0536</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1362</v>
+        <v>0.0536</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0164</v>
+        <v>-0.0056</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0057</v>
+        <v>-0.0019</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6454</v>
+        <v>-0.6268</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0164</v>
+        <v>-0.0056</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0164</v>
+        <v>-0.0056</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0164</v>
+        <v>-0.0056</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0164</v>
+        <v>-0.0056</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0164</v>
+        <v>-0.0056</v>
       </c>
       <c r="N30" t="n">
         <v>207</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0225</v>
+        <v>-0.025</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6674</v>
+        <v>-0.6572</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>207</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1912</v>
+        <v>-0.226</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.7271</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1912</v>
+        <v>-0.226</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1912</v>
+        <v>-0.226</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1912</v>
+        <v>-0.226</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1912</v>
+        <v>-0.226</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1912</v>
+        <v>-0.226</v>
       </c>
       <c r="N32" t="n">
         <v>104</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.225</v>
+        <v>-0.2594</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0897</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7396</v>
+        <v>-0.7423</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.225</v>
+        <v>-0.2594</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.225</v>
+        <v>-0.2594</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.225</v>
+        <v>-0.2594</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.225</v>
+        <v>-0.2594</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.225</v>
+        <v>-0.2594</v>
       </c>
       <c r="N33" t="n">
         <v>189</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2575</v>
+        <v>-0.3709</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.089</v>
+        <v>-0.1283</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7543</v>
+        <v>-0.793</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2575</v>
+        <v>-0.3709</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2575</v>
+        <v>-0.3709</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2575</v>
+        <v>-0.3709</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2575</v>
+        <v>-0.3709</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2575</v>
+        <v>-0.3709</v>
       </c>
       <c r="N34" t="n">
         <v>125</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4408</v>
+        <v>-0.5265</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1524</v>
+        <v>-0.1821</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.837</v>
+        <v>-0.8639</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4408</v>
+        <v>-0.5265</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4408</v>
+        <v>-0.5265</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4408</v>
+        <v>-0.5265</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4408</v>
+        <v>-0.5265</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4408</v>
+        <v>-0.5265</v>
       </c>
       <c r="N35" t="n">
         <v>125</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4762</v>
+        <v>-0.5308</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1647</v>
+        <v>-0.1836</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.853</v>
+        <v>-0.8658</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4762</v>
+        <v>-0.5308</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4762</v>
+        <v>-0.5308</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4762</v>
+        <v>-0.5308</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4762</v>
+        <v>-0.5308</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4762</v>
+        <v>-0.5308</v>
       </c>
       <c r="N36" t="n">
         <v>125</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5345</v>
+        <v>-0.5698</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1848</v>
+        <v>-0.197</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8793</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5345</v>
+        <v>-0.5698</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5345</v>
+        <v>-0.5698</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5345</v>
+        <v>-0.5698</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5345</v>
+        <v>-0.5698</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5345</v>
+        <v>-0.5698</v>
       </c>
       <c r="N37" t="n">
         <v>104</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.5773</v>
+        <v>-0.5803</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1996</v>
+        <v>-0.2007</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8986</v>
+        <v>-0.8884</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5773</v>
+        <v>-0.5803</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5773</v>
+        <v>-0.5803</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5773</v>
+        <v>-0.5803</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5773</v>
+        <v>-0.5803</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.5773</v>
+        <v>-0.5803</v>
       </c>
       <c r="N38" t="n">
         <v>86</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9405</v>
+        <v>-0.9674</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3252</v>
+        <v>-0.3345</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0626</v>
+        <v>-1.0646</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9405</v>
+        <v>-0.9674</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9405</v>
+        <v>-0.9674</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9405</v>
+        <v>-0.9674</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9405</v>
+        <v>-0.9674</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9405</v>
+        <v>-0.9674</v>
       </c>
       <c r="N39" t="n">
         <v>39</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2253</v>
+        <v>-1.2667</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4237</v>
+        <v>-0.438</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1912</v>
+        <v>-1.2008</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2253</v>
+        <v>-1.2667</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2253</v>
+        <v>-1.2667</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2253</v>
+        <v>-1.2667</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2253</v>
+        <v>-1.2667</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2253</v>
+        <v>-1.2667</v>
       </c>
       <c r="N40" t="n">
         <v>104</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.887</v>
+        <v>-1.8743</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6525</v>
+        <v>-0.6482</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4899</v>
+        <v>-1.4774</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.887</v>
+        <v>-1.8743</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3259</v>
+        <v>-1.28</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5611</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3259</v>
+        <v>-1.28</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6894</v>
+        <v>-0.6912</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5611</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>182</v>
@@ -2323,7 +2323,7 @@
         <v>52</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2505</v>
+        <v>-1.2855</v>
       </c>
       <c r="N41" t="n">
         <v>234</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-3.3796</v>
+        <v>-3.2206</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.1687</v>
+        <v>-1.1137</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.1637</v>
+        <v>-2.0903</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.3796</v>
+        <v>-3.2206</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.3796</v>
+        <v>-2.2206</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.3796</v>
+        <v>-2.2206</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.2373</v>
+        <v>-1.1991</v>
       </c>
       <c r="J42" t="n">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>69</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.2373</v>
+        <v>-2.1991</v>
       </c>
       <c r="N42" t="n">
         <v>279</v>
@@ -2475,10 +2475,10 @@
         <v>0.83</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1436</v>
+        <v>-0.1717</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.5848</v>
+        <v>-3.0906</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1997</v>
+        <v>-0.2262</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.5946</v>
+        <v>-4.0716</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3759</v>
+        <v>-0.3955</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.7662</v>
+        <v>-7.119</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.58</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.394</v>
+        <v>-0.4127</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.092</v>
+        <v>-7.4286</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.3</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6587</v>
+        <v>-0.6586</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.8566</v>
+        <v>-11.8548</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.94</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5706</v>
+        <v>1.7158</v>
       </c>
       <c r="J7" t="n">
-        <v>28.2708</v>
+        <v>30.8844</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.93</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5598</v>
+        <v>1.7043</v>
       </c>
       <c r="J8" t="n">
-        <v>28.0764</v>
+        <v>30.6774</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.53</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1171</v>
+        <v>1.1213</v>
       </c>
       <c r="J9" t="n">
-        <v>20.1078</v>
+        <v>20.1834</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.46</v>
       </c>
       <c r="I10" t="n">
-        <v>1.031</v>
+        <v>0.9981</v>
       </c>
       <c r="J10" t="n">
-        <v>18.558</v>
+        <v>17.9658</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.34</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7992</v>
+        <v>0.7739</v>
       </c>
       <c r="J11" t="n">
-        <v>14.3856</v>
+        <v>13.9302</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>0.86</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0876</v>
+        <v>-0.1208</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6644</v>
+        <v>-2.2952</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.62</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3504</v>
+        <v>-0.3726</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.6576</v>
+        <v>-7.0794</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.58</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3874</v>
+        <v>-0.4077</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.3606</v>
+        <v>-7.7463</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.57</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3959</v>
+        <v>-0.4159</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.5221</v>
+        <v>-7.9021</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.22</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7296</v>
+        <v>-0.724</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.8624</v>
+        <v>-13.756</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>2.02</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6663</v>
+        <v>1.8147</v>
       </c>
       <c r="J17" t="n">
-        <v>31.6597</v>
+        <v>34.4793</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4133</v>
+        <v>1.5395</v>
       </c>
       <c r="J18" t="n">
-        <v>26.8527</v>
+        <v>29.2505</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.73</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3464</v>
+        <v>1.4522</v>
       </c>
       <c r="J19" t="n">
-        <v>25.5816</v>
+        <v>27.5918</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6495</v>
+        <v>0.6403</v>
       </c>
       <c r="J20" t="n">
-        <v>12.3405</v>
+        <v>12.1657</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>1.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3282</v>
+        <v>0.3521</v>
       </c>
       <c r="J21" t="n">
-        <v>6.2358</v>
+        <v>6.6899</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.18</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3866</v>
+        <v>0.3883</v>
       </c>
       <c r="J22" t="n">
-        <v>11.598</v>
+        <v>11.649</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3497</v>
+        <v>0.3537</v>
       </c>
       <c r="J23" t="n">
-        <v>10.491</v>
+        <v>10.611</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3497</v>
+        <v>0.3537</v>
       </c>
       <c r="J24" t="n">
-        <v>10.491</v>
+        <v>10.611</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1313</v>
+        <v>0.1422</v>
       </c>
       <c r="J25" t="n">
-        <v>3.939</v>
+        <v>4.266</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.72</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3231</v>
+        <v>-0.3338</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.693</v>
+        <v>-10.014</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.44</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0845</v>
+        <v>1.0513</v>
       </c>
       <c r="J27" t="n">
-        <v>32.535</v>
+        <v>31.539</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5777</v>
+        <v>0.5572</v>
       </c>
       <c r="J28" t="n">
-        <v>17.331</v>
+        <v>16.716</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5023</v>
+        <v>0.4895</v>
       </c>
       <c r="J29" t="n">
-        <v>15.069</v>
+        <v>14.685</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0276</v>
+        <v>-0.0189</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.828</v>
+        <v>-0.5669999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.706</v>
+        <v>-0.6565</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.18</v>
+        <v>-19.695</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6997</v>
+        <v>0.775</v>
       </c>
       <c r="J32" t="n">
-        <v>18.8919</v>
+        <v>20.925</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.31</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6193</v>
+        <v>0.6869</v>
       </c>
       <c r="J33" t="n">
-        <v>16.7211</v>
+        <v>18.5463</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5647</v>
+        <v>0.6266</v>
       </c>
       <c r="J34" t="n">
-        <v>15.2469</v>
+        <v>16.9182</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.11</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3289</v>
+        <v>0.3369</v>
       </c>
       <c r="J35" t="n">
-        <v>8.8803</v>
+        <v>9.096299999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.91</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3727</v>
+        <v>-0.3521</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.0629</v>
+        <v>-9.5067</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4152</v>
+        <v>0.4548</v>
       </c>
       <c r="J37" t="n">
-        <v>11.2104</v>
+        <v>12.2796</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="J38" t="n">
-        <v>10.0143</v>
+        <v>10.5759</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1252</v>
+        <v>0.1312</v>
       </c>
       <c r="J39" t="n">
-        <v>3.3804</v>
+        <v>3.5424</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.234</v>
+        <v>-0.2485</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.318</v>
+        <v>-6.7095</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4522</v>
+        <v>-0.4598</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.2094</v>
+        <v>-12.4146</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.63</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9912</v>
+        <v>1.0961</v>
       </c>
       <c r="J42" t="n">
-        <v>24.78</v>
+        <v>27.4025</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7362</v>
+        <v>0.8209</v>
       </c>
       <c r="J43" t="n">
-        <v>18.405</v>
+        <v>20.5225</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.41</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7239</v>
+        <v>0.8075</v>
       </c>
       <c r="J44" t="n">
-        <v>18.0975</v>
+        <v>20.1875</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.38</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6871</v>
+        <v>0.767</v>
       </c>
       <c r="J45" t="n">
-        <v>17.1775</v>
+        <v>19.175</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>0.007</v>
+        <v>0.0394</v>
       </c>
       <c r="J46" t="n">
-        <v>0.175</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>0.91</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0813</v>
+        <v>-0.1031</v>
       </c>
       <c r="J47" t="n">
-        <v>-2.0325</v>
+        <v>-2.5775</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.8</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2043</v>
+        <v>-0.2256</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.1075</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3271</v>
+        <v>-0.3458</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.1775</v>
+        <v>-8.645</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3271</v>
+        <v>-0.3458</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.1775</v>
+        <v>-8.645</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4392</v>
+        <v>-0.4526</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.98</v>
+        <v>-11.315</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4952</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>12.38</v>
+        <v>13.6475</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>0.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1419</v>
+        <v>-0.1584</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.5475</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.72</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2995</v>
+        <v>-0.3153</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.4875</v>
+        <v>-7.8825</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3376</v>
+        <v>-0.3522</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.44</v>
+        <v>-8.805</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.366</v>
+        <v>-0.3795</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.15</v>
+        <v>-9.487500000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.71</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6359</v>
+        <v>0.7289</v>
       </c>
       <c r="J57" t="n">
-        <v>15.8975</v>
+        <v>18.2225</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4452</v>
+        <v>0.5068</v>
       </c>
       <c r="J58" t="n">
-        <v>11.13</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0756</v>
+        <v>0.0922</v>
       </c>
       <c r="J59" t="n">
-        <v>1.89</v>
+        <v>2.305</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0406</v>
+        <v>-0.0407</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.015</v>
+        <v>-1.0175</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.178</v>
+        <v>-0.1864</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.45</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9181</v>
+        <v>1.0158</v>
       </c>
       <c r="J62" t="n">
-        <v>19.2801</v>
+        <v>21.3318</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8565</v>
+        <v>0.9495</v>
       </c>
       <c r="J63" t="n">
-        <v>17.9865</v>
+        <v>19.9395</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5253</v>
+        <v>0.5857</v>
       </c>
       <c r="J64" t="n">
-        <v>11.0313</v>
+        <v>12.2997</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>1.25</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5253</v>
+        <v>0.5857</v>
       </c>
       <c r="J65" t="n">
-        <v>11.0313</v>
+        <v>12.2997</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.99</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1305</v>
+        <v>-0.1123</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.7405</v>
+        <v>-2.3583</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3498</v>
+        <v>0.3414</v>
       </c>
       <c r="J67" t="n">
-        <v>7.3458</v>
+        <v>7.1694</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>0.84</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1717</v>
+        <v>-0.1915</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.6057</v>
+        <v>-4.0215</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>0.73</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.278</v>
+        <v>-0.2967</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.838</v>
+        <v>-6.2307</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.66</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.344</v>
+        <v>-0.3606</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.224</v>
+        <v>-7.5726</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.51</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4841</v>
+        <v>-0.4936</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.1661</v>
+        <v>-10.3656</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9356</v>
+        <v>1.0382</v>
       </c>
       <c r="J72" t="n">
-        <v>21.5188</v>
+        <v>23.8786</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.56</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8999</v>
+        <v>0.9998</v>
       </c>
       <c r="J73" t="n">
-        <v>20.6977</v>
+        <v>22.9954</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8879</v>
+        <v>0.9869</v>
       </c>
       <c r="J74" t="n">
-        <v>20.4217</v>
+        <v>22.6987</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.45</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7679</v>
+        <v>0.8568</v>
       </c>
       <c r="J75" t="n">
-        <v>17.6617</v>
+        <v>19.7064</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3319</v>
+        <v>-0.3024</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.6337</v>
+        <v>-6.9552</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>0.85</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.118</v>
+        <v>-0.1471</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.714</v>
+        <v>-3.3833</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>0.85</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.118</v>
+        <v>-0.1471</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.714</v>
+        <v>-3.3833</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.65</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3307</v>
+        <v>-0.3522</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.6061</v>
+        <v>-8.1006</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.38</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5812</v>
+        <v>-0.5876</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.3676</v>
+        <v>-13.5148</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.33</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6291</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.4693</v>
+        <v>-14.5268</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2517</v>
+        <v>1.2273</v>
       </c>
       <c r="J82" t="n">
-        <v>28.7891</v>
+        <v>28.2279</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.45</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0541</v>
+        <v>1.0106</v>
       </c>
       <c r="J83" t="n">
-        <v>24.2443</v>
+        <v>23.2438</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.34</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8565</v>
+        <v>0.8135</v>
       </c>
       <c r="J84" t="n">
-        <v>19.6995</v>
+        <v>18.7105</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.303</v>
+        <v>0.317</v>
       </c>
       <c r="J85" t="n">
-        <v>6.969</v>
+        <v>7.291</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>1.08</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2169</v>
+        <v>0.2372</v>
       </c>
       <c r="J86" t="n">
-        <v>4.9887</v>
+        <v>5.4556</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.16</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4212</v>
+        <v>0.4061</v>
       </c>
       <c r="J87" t="n">
-        <v>9.6876</v>
+        <v>9.340299999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.07</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2304</v>
+        <v>0.2257</v>
       </c>
       <c r="J88" t="n">
-        <v>5.2992</v>
+        <v>5.1911</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2111</v>
+        <v>-0.2286</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.8553</v>
+        <v>-5.2578</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.68</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3368</v>
+        <v>-0.3516</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.7464</v>
+        <v>-8.0868</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4673</v>
+        <v>-0.4762</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.7479</v>
+        <v>-10.9526</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.57</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8365</v>
+        <v>0.7976</v>
       </c>
       <c r="J92" t="n">
-        <v>23.422</v>
+        <v>22.3328</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>0.87</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1616</v>
+        <v>-0.1761</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.5248</v>
+        <v>-4.9308</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1721</v>
+        <v>-0.1868</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.8188</v>
+        <v>-5.2304</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2731</v>
+        <v>-0.2871</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.6468</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.71</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3214</v>
+        <v>-0.3342</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.9992</v>
+        <v>-9.3576</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.34</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4622</v>
+        <v>0.4701</v>
       </c>
       <c r="J97" t="n">
-        <v>12.9416</v>
+        <v>13.1628</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.17</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2542</v>
+        <v>0.2697</v>
       </c>
       <c r="J98" t="n">
-        <v>7.1176</v>
+        <v>7.5516</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.15</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2283</v>
+        <v>0.2441</v>
       </c>
       <c r="J99" t="n">
-        <v>6.3924</v>
+        <v>6.8348</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1039</v>
+        <v>0.1181</v>
       </c>
       <c r="J100" t="n">
-        <v>2.9092</v>
+        <v>3.3068</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2406</v>
+        <v>-0.2516</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.7368</v>
+        <v>-7.0448</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0753</v>
+        <v>1.031</v>
       </c>
       <c r="J102" t="n">
-        <v>26.8825</v>
+        <v>25.775</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8142</v>
+        <v>0.7716</v>
       </c>
       <c r="J103" t="n">
-        <v>20.355</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7222</v>
+        <v>0.6904</v>
       </c>
       <c r="J104" t="n">
-        <v>18.055</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3006</v>
+        <v>0.3089</v>
       </c>
       <c r="J105" t="n">
-        <v>7.515</v>
+        <v>7.7225</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3762</v>
+        <v>-0.3546</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.404999999999999</v>
+        <v>-8.865</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4632</v>
+        <v>0.4517</v>
       </c>
       <c r="J107" t="n">
-        <v>11.58</v>
+        <v>11.2925</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.03</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1071</v>
+        <v>0.111</v>
       </c>
       <c r="J108" t="n">
-        <v>2.6775</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0145</v>
+        <v>-0.0206</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.3625</v>
+        <v>-0.515</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.85</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.18</v>
+        <v>-0.1953</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.5</v>
+        <v>-4.8825</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.59</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.431</v>
+        <v>-0.4401</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.775</v>
+        <v>-11.0025</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4537</v>
+        <v>0.4338</v>
       </c>
       <c r="J112" t="n">
-        <v>12.2499</v>
+        <v>11.7126</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.03</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1428</v>
+        <v>0.1371</v>
       </c>
       <c r="J113" t="n">
-        <v>3.8556</v>
+        <v>3.7017</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0684</v>
+        <v>-0.0839</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.8468</v>
+        <v>-2.2653</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.65</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3618</v>
+        <v>-0.3763</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.768599999999999</v>
+        <v>-10.1601</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.35</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.637</v>
+        <v>-0.6355</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.199</v>
+        <v>-17.1585</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1415</v>
+        <v>1.1092</v>
       </c>
       <c r="J117" t="n">
-        <v>30.8205</v>
+        <v>29.9484</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.49</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1044</v>
+        <v>1.0689</v>
       </c>
       <c r="J118" t="n">
-        <v>29.8188</v>
+        <v>28.8603</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9954</v>
+        <v>0.9439</v>
       </c>
       <c r="J119" t="n">
-        <v>26.8758</v>
+        <v>25.4853</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>1.29</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7487</v>
+        <v>0.7178</v>
       </c>
       <c r="J120" t="n">
-        <v>20.2149</v>
+        <v>19.3806</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4879</v>
+        <v>-0.4516</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.1733</v>
+        <v>-12.1932</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.26</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3718</v>
+        <v>0.3829</v>
       </c>
       <c r="J122" t="n">
-        <v>10.4104</v>
+        <v>10.7212</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.232</v>
+        <v>0.2469</v>
       </c>
       <c r="J123" t="n">
-        <v>6.496</v>
+        <v>6.9132</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2053</v>
+        <v>0.2205</v>
       </c>
       <c r="J124" t="n">
-        <v>5.7484</v>
+        <v>6.174</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>2.0972</v>
+        <v>2.4332</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2377</v>
+        <v>-0.2493</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.6556</v>
+        <v>-6.9804</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5402</v>
+        <v>0.5327</v>
       </c>
       <c r="J127" t="n">
-        <v>15.1256</v>
+        <v>14.9156</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1668</v>
+        <v>0.1778</v>
       </c>
       <c r="J128" t="n">
-        <v>4.6704</v>
+        <v>4.9784</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.04</v>
       </c>
       <c r="I129" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="J129" t="n">
-        <v>2.3688</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1493</v>
+        <v>-0.1614</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.1804</v>
+        <v>-4.5192</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.8</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2431</v>
+        <v>-0.2556</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.8068</v>
+        <v>-7.1568</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.09</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2804</v>
+        <v>0.2726</v>
       </c>
       <c r="J132" t="n">
-        <v>6.1688</v>
+        <v>5.9972</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0828</v>
+        <v>-0.0984</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.8216</v>
+        <v>-2.1648</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.89</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1289</v>
+        <v>-0.1457</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.8358</v>
+        <v>-3.2054</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.86</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1607</v>
+        <v>-0.1781</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.5354</v>
+        <v>-3.9182</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5662</v>
+        <v>-0.5693</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.4564</v>
+        <v>-12.5246</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.74</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4099</v>
+        <v>1.3949</v>
       </c>
       <c r="J137" t="n">
-        <v>31.0178</v>
+        <v>30.6878</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.28</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7276</v>
+        <v>0.6989</v>
       </c>
       <c r="J138" t="n">
-        <v>16.0072</v>
+        <v>15.3758</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.21</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5639</v>
+        <v>0.553</v>
       </c>
       <c r="J139" t="n">
-        <v>12.4058</v>
+        <v>12.166</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>1.18</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4897</v>
+        <v>0.4863</v>
       </c>
       <c r="J140" t="n">
-        <v>10.7734</v>
+        <v>10.6986</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3864</v>
+        <v>0.3928</v>
       </c>
       <c r="J141" t="n">
-        <v>8.5008</v>
+        <v>8.6416</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.12</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3012</v>
+        <v>0.3016</v>
       </c>
       <c r="J142" t="n">
-        <v>8.4336</v>
+        <v>8.444800000000001</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.076</v>
+        <v>0.0805</v>
       </c>
       <c r="J143" t="n">
-        <v>2.128</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.047</v>
+        <v>0.0499</v>
       </c>
       <c r="J144" t="n">
-        <v>1.316</v>
+        <v>1.3972</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0166</v>
+        <v>-0.0222</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.4648</v>
+        <v>-0.6216</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4146</v>
+        <v>-0.4242</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.6088</v>
+        <v>-11.8776</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0099</v>
+        <v>0.9564</v>
       </c>
       <c r="J147" t="n">
-        <v>28.2772</v>
+        <v>26.7792</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.32</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8266</v>
+        <v>0.7844</v>
       </c>
       <c r="J148" t="n">
-        <v>23.1448</v>
+        <v>21.9632</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.25</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6446</v>
       </c>
       <c r="J149" t="n">
-        <v>18.7292</v>
+        <v>18.0488</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.16</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4525</v>
+        <v>0.4499</v>
       </c>
       <c r="J150" t="n">
-        <v>12.67</v>
+        <v>12.5972</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>1.1</v>
       </c>
       <c r="I151" t="n">
-        <v>0.2912</v>
+        <v>0.3024</v>
       </c>
       <c r="J151" t="n">
-        <v>8.153600000000001</v>
+        <v>8.4672</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3676</v>
+        <v>0.3667</v>
       </c>
       <c r="J152" t="n">
-        <v>11.028</v>
+        <v>11.001</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.01</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0395</v>
+        <v>0.0446</v>
       </c>
       <c r="J153" t="n">
-        <v>1.185</v>
+        <v>1.338</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0351</v>
+        <v>-0.042</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.053</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.9</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1329</v>
+        <v>-0.1459</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.987</v>
+        <v>-4.377</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1439</v>
+        <v>-0.1572</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.317</v>
+        <v>-4.716</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9067</v>
+        <v>0.8484</v>
       </c>
       <c r="J157" t="n">
-        <v>27.201</v>
+        <v>25.452</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4981</v>
+        <v>0.4866</v>
       </c>
       <c r="J158" t="n">
-        <v>14.943</v>
+        <v>14.598</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.473</v>
+        <v>0.4638</v>
       </c>
       <c r="J159" t="n">
-        <v>14.19</v>
+        <v>13.914</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2887</v>
+        <v>0.294</v>
       </c>
       <c r="J160" t="n">
-        <v>8.661</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3279</v>
+        <v>-0.3139</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.837</v>
+        <v>-9.417</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8423</v>
+        <v>0.7911</v>
       </c>
       <c r="J162" t="n">
-        <v>23.5844</v>
+        <v>22.1508</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6505</v>
+        <v>0.6223</v>
       </c>
       <c r="J163" t="n">
-        <v>18.214</v>
+        <v>17.4244</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6014</v>
+        <v>0.5786</v>
       </c>
       <c r="J164" t="n">
-        <v>16.8392</v>
+        <v>16.2008</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1967</v>
+        <v>-0.1912</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.5076</v>
+        <v>-5.3536</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.9</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3832</v>
+        <v>-0.3659</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.7296</v>
+        <v>-10.2452</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.43</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8325</v>
+        <v>0.792</v>
       </c>
       <c r="J167" t="n">
-        <v>23.31</v>
+        <v>22.176</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.223</v>
+        <v>0.2307</v>
       </c>
       <c r="J168" t="n">
-        <v>6.244</v>
+        <v>6.4596</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.86</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1788</v>
+        <v>-0.192</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.0064</v>
+        <v>-5.376</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1997</v>
+        <v>-0.213</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.5916</v>
+        <v>-5.964</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.84</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1997</v>
+        <v>-0.213</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.5916</v>
+        <v>-5.964</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.64</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2796</v>
+        <v>1.2586</v>
       </c>
       <c r="J172" t="n">
-        <v>29.4308</v>
+        <v>28.9478</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.36</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8934</v>
+        <v>0.8472</v>
       </c>
       <c r="J173" t="n">
-        <v>20.5482</v>
+        <v>19.4856</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.29</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7415</v>
+        <v>0.7129</v>
       </c>
       <c r="J174" t="n">
-        <v>17.0545</v>
+        <v>16.3967</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.28</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7188</v>
+        <v>0.6928</v>
       </c>
       <c r="J175" t="n">
-        <v>16.5324</v>
+        <v>15.9344</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>1.22</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5779</v>
+        <v>0.5676</v>
       </c>
       <c r="J176" t="n">
-        <v>13.2917</v>
+        <v>13.0548</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.04</v>
       </c>
       <c r="I177" t="n">
-        <v>0.201</v>
+        <v>0.1867</v>
       </c>
       <c r="J177" t="n">
-        <v>4.623</v>
+        <v>4.2941</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.91</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0917</v>
+        <v>-0.1113</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.1091</v>
+        <v>-2.5599</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.76</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2493</v>
+        <v>-0.2687</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.7339</v>
+        <v>-6.1801</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.67</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3334</v>
+        <v>-0.3506</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.6682</v>
+        <v>-8.063800000000001</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.43</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5568</v>
+        <v>-0.5619</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.8064</v>
+        <v>-12.9237</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.36</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4701</v>
+        <v>0.4804</v>
       </c>
       <c r="J182" t="n">
-        <v>12.6927</v>
+        <v>12.9708</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.3</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4011</v>
+        <v>0.4146</v>
       </c>
       <c r="J183" t="n">
-        <v>10.8297</v>
+        <v>11.1942</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2588</v>
+        <v>0.2762</v>
       </c>
       <c r="J184" t="n">
-        <v>6.9876</v>
+        <v>7.4574</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.15</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2212</v>
+        <v>0.2389</v>
       </c>
       <c r="J185" t="n">
-        <v>5.9724</v>
+        <v>6.4503</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1074</v>
+        <v>-0.114</v>
       </c>
       <c r="J186" t="n">
-        <v>-2.8998</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8532</v>
+        <v>0.8137</v>
       </c>
       <c r="J187" t="n">
-        <v>23.0364</v>
+        <v>21.9699</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3429</v>
+        <v>0.3451</v>
       </c>
       <c r="J188" t="n">
-        <v>9.2583</v>
+        <v>9.3177</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.85</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1847</v>
+        <v>-0.1989</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.9869</v>
+        <v>-5.3703</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.77</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2655</v>
+        <v>-0.2792</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.1685</v>
+        <v>-7.5384</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.45</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5613</v>
+        <v>-0.5628</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.1551</v>
+        <v>-15.1956</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.31</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6706</v>
       </c>
       <c r="J192" t="n">
-        <v>17.805</v>
+        <v>16.765</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.89</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1294</v>
+        <v>-0.1461</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.235</v>
+        <v>-3.6525</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.8</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.22</v>
+        <v>-0.2376</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.5</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3546</v>
+        <v>-0.3689</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.865</v>
+        <v>-9.2225</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4479</v>
+        <v>-0.4579</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.1975</v>
+        <v>-11.4475</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.04</v>
+        <v>0.9908</v>
       </c>
       <c r="J197" t="n">
-        <v>26</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.23</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6236</v>
+        <v>0.6039</v>
       </c>
       <c r="J198" t="n">
-        <v>15.59</v>
+        <v>15.0975</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.22</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6002</v>
+        <v>0.5829</v>
       </c>
       <c r="J199" t="n">
-        <v>15.005</v>
+        <v>14.5725</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.2</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5523</v>
+        <v>0.5399</v>
       </c>
       <c r="J200" t="n">
-        <v>13.8075</v>
+        <v>13.4975</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>1.16</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4525</v>
+        <v>0.4499</v>
       </c>
       <c r="J201" t="n">
-        <v>11.3125</v>
+        <v>11.2475</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.51</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9817</v>
+        <v>0.9275</v>
       </c>
       <c r="J202" t="n">
-        <v>33.3778</v>
+        <v>31.535</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.96</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0601</v>
+        <v>-0.0702</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.0434</v>
+        <v>-2.3868</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.92</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1077</v>
+        <v>-0.1206</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.6618</v>
+        <v>-4.1004</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2544</v>
+        <v>-0.2686</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.6496</v>
+        <v>-9.132400000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3882</v>
+        <v>-0.3986</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.1988</v>
+        <v>-13.5524</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3953</v>
+        <v>1.3676</v>
       </c>
       <c r="J207" t="n">
-        <v>47.4402</v>
+        <v>46.4984</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.37</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9883</v>
+        <v>0.9233</v>
       </c>
       <c r="J208" t="n">
-        <v>33.6022</v>
+        <v>31.3922</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.85</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.5134</v>
+        <v>-0.4863</v>
       </c>
       <c r="J209" t="n">
-        <v>-17.4556</v>
+        <v>-16.5342</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6975</v>
+        <v>-0.6505</v>
       </c>
       <c r="J210" t="n">
-        <v>-23.715</v>
+        <v>-22.117</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.76</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7484</v>
+        <v>-0.6953</v>
       </c>
       <c r="J211" t="n">
-        <v>-25.4456</v>
+        <v>-23.6402</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.23</v>
       </c>
       <c r="I212" t="n">
-        <v>0.379</v>
+        <v>0.3804</v>
       </c>
       <c r="J212" t="n">
-        <v>10.991</v>
+        <v>11.0316</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.22</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3652</v>
+        <v>0.3673</v>
       </c>
       <c r="J213" t="n">
-        <v>10.5908</v>
+        <v>10.6517</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.111</v>
+        <v>-0.1231</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.219</v>
+        <v>-3.5699</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1873</v>
+        <v>-0.2009</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.4317</v>
+        <v>-5.8261</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2876</v>
+        <v>-0.3004</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.340400000000001</v>
+        <v>-8.711600000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4556</v>
+        <v>0.4629</v>
       </c>
       <c r="J217" t="n">
-        <v>13.2124</v>
+        <v>13.4241</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2315</v>
+        <v>0.2465</v>
       </c>
       <c r="J218" t="n">
-        <v>6.7135</v>
+        <v>7.1485</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1216</v>
+        <v>0.1356</v>
       </c>
       <c r="J219" t="n">
-        <v>3.5264</v>
+        <v>3.9324</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0281</v>
+        <v>-0.031</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.8149</v>
+        <v>-0.899</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.176</v>
+        <v>-0.1873</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.104</v>
+        <v>-5.4317</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.19</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5642</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>16.3618</v>
+        <v>15.7412</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.487</v>
+        <v>0.4734</v>
       </c>
       <c r="J223" t="n">
-        <v>14.123</v>
+        <v>13.7286</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3809</v>
+        <v>0.3769</v>
       </c>
       <c r="J224" t="n">
-        <v>11.0461</v>
+        <v>10.9301</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1506</v>
+        <v>-0.1496</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.3674</v>
+        <v>-4.3384</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1855</v>
+        <v>-0.1833</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.3795</v>
+        <v>-5.3157</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.16</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3589</v>
+        <v>0.3604</v>
       </c>
       <c r="J227" t="n">
-        <v>10.4081</v>
+        <v>10.4516</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.282</v>
+        <v>0.2876</v>
       </c>
       <c r="J228" t="n">
-        <v>8.178000000000001</v>
+        <v>8.340400000000001</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2217</v>
+        <v>0.2297</v>
       </c>
       <c r="J229" t="n">
-        <v>6.4293</v>
+        <v>6.6613</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.065</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J230" t="n">
-        <v>-1.885</v>
+        <v>-2.1431</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.76</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2806</v>
+        <v>-0.293</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.1374</v>
+        <v>-8.497</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>1.064</v>
+        <v>1.0171</v>
       </c>
       <c r="J232" t="n">
-        <v>26.6</v>
+        <v>25.4275</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.34</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8849</v>
+        <v>0.833</v>
       </c>
       <c r="J233" t="n">
-        <v>22.1225</v>
+        <v>20.825</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.13</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3847</v>
+        <v>0.3858</v>
       </c>
       <c r="J234" t="n">
-        <v>9.6175</v>
+        <v>9.645</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.09</v>
       </c>
       <c r="I235" t="n">
-        <v>0.274</v>
+        <v>0.2838</v>
       </c>
       <c r="J235" t="n">
-        <v>6.85</v>
+        <v>7.095</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0486</v>
+        <v>-0.0336</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.215</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.34</v>
       </c>
       <c r="I237" t="n">
-        <v>0.709</v>
+        <v>0.6768</v>
       </c>
       <c r="J237" t="n">
-        <v>17.725</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.09</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2399</v>
+        <v>0.2429</v>
       </c>
       <c r="J238" t="n">
-        <v>5.9975</v>
+        <v>6.0725</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1286</v>
+        <v>-0.1426</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.215</v>
+        <v>-3.565</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2626</v>
+        <v>-0.2769</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.565</v>
+        <v>-6.9225</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3866</v>
+        <v>-0.3974</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.664999999999999</v>
+        <v>-9.935</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4745</v>
+        <v>0.4492</v>
       </c>
       <c r="J242" t="n">
-        <v>10.9135</v>
+        <v>10.3316</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>0.84</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1752</v>
+        <v>-0.1942</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.0296</v>
+        <v>-4.4666</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.73</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2809</v>
+        <v>-0.299</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.4607</v>
+        <v>-6.877</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.61</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3942</v>
+        <v>-0.4081</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.066599999999999</v>
+        <v>-9.3863</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.61</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3942</v>
+        <v>-0.4081</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.066599999999999</v>
+        <v>-9.3863</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2412</v>
+        <v>1.2158</v>
       </c>
       <c r="J247" t="n">
-        <v>28.5476</v>
+        <v>27.9634</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.47</v>
       </c>
       <c r="I248" t="n">
-        <v>1.0808</v>
+        <v>1.0419</v>
       </c>
       <c r="J248" t="n">
-        <v>24.8584</v>
+        <v>23.9637</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>1.41</v>
       </c>
       <c r="I249" t="n">
-        <v>0.9969</v>
+        <v>0.9452</v>
       </c>
       <c r="J249" t="n">
-        <v>22.9287</v>
+        <v>21.7396</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>1.29</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7499</v>
+        <v>0.7187</v>
       </c>
       <c r="J250" t="n">
-        <v>17.2477</v>
+        <v>16.5301</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7504</v>
+        <v>-0.6878</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.2592</v>
+        <v>-15.8194</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.7</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1381</v>
+        <v>1.1124</v>
       </c>
       <c r="J252" t="n">
-        <v>34.143</v>
+        <v>33.372</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1511</v>
+        <v>0.1626</v>
       </c>
       <c r="J253" t="n">
-        <v>4.533</v>
+        <v>4.878</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0955</v>
+        <v>-0.1047</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.865</v>
+        <v>-3.141</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0955</v>
+        <v>-0.1047</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.865</v>
+        <v>-3.141</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3343</v>
+        <v>-0.3444</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.029</v>
+        <v>-10.332</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4479</v>
+        <v>0.4351</v>
       </c>
       <c r="J257" t="n">
-        <v>13.437</v>
+        <v>13.053</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.08</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2795</v>
+        <v>0.2804</v>
       </c>
       <c r="J258" t="n">
-        <v>8.385</v>
+        <v>8.412000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.04</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1565</v>
+        <v>0.1635</v>
       </c>
       <c r="J259" t="n">
-        <v>4.695</v>
+        <v>4.905</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>1.02</v>
       </c>
       <c r="I260" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0954</v>
       </c>
       <c r="J260" t="n">
-        <v>2.625</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.9</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3592</v>
+        <v>-0.3492</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.776</v>
+        <v>-10.476</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.21</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4862</v>
+        <v>0.4721</v>
       </c>
       <c r="J262" t="n">
-        <v>14.586</v>
+        <v>14.163</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>0.97</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0434</v>
+        <v>-0.0532</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.302</v>
+        <v>-1.596</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0568</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.704</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.094</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.448</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4847</v>
+        <v>-0.4913</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.541</v>
+        <v>-14.739</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.5</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1444</v>
+        <v>1.1069</v>
       </c>
       <c r="J267" t="n">
-        <v>34.332</v>
+        <v>33.207</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.18</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5143</v>
+        <v>0.5032</v>
       </c>
       <c r="J268" t="n">
-        <v>15.429</v>
+        <v>15.096</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>1.16</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4649</v>
+        <v>0.4584</v>
       </c>
       <c r="J269" t="n">
-        <v>13.947</v>
+        <v>13.752</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>1.15</v>
       </c>
       <c r="I270" t="n">
-        <v>0.4395</v>
+        <v>0.4352</v>
       </c>
       <c r="J270" t="n">
-        <v>13.185</v>
+        <v>13.056</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.95</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2474</v>
+        <v>-0.2352</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.422</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.47</v>
       </c>
       <c r="I272" t="n">
-        <v>1.006</v>
+        <v>0.9408</v>
       </c>
       <c r="J272" t="n">
-        <v>25.15</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>0.75</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.265</v>
+        <v>-0.2828</v>
       </c>
       <c r="J273" t="n">
-        <v>-6.625</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>0.7</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3128</v>
+        <v>-0.3293</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.82</v>
+        <v>-8.2325</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3977</v>
+        <v>-0.4108</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.942500000000001</v>
+        <v>-10.27</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.55</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4534</v>
+        <v>-0.4638</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.335</v>
+        <v>-11.595</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.79</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4566</v>
+        <v>1.4462</v>
       </c>
       <c r="J277" t="n">
-        <v>36.415</v>
+        <v>36.155</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>1.56</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1829</v>
+        <v>1.1552</v>
       </c>
       <c r="J278" t="n">
-        <v>29.5725</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>1.17</v>
       </c>
       <c r="I279" t="n">
-        <v>0.4533</v>
+        <v>0.4558</v>
       </c>
       <c r="J279" t="n">
-        <v>11.3325</v>
+        <v>11.395</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>1.16</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4276</v>
+        <v>0.4326</v>
       </c>
       <c r="J280" t="n">
-        <v>10.69</v>
+        <v>10.815</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>1.12</v>
       </c>
       <c r="I281" t="n">
-        <v>0.3212</v>
+        <v>0.3357</v>
       </c>
       <c r="J281" t="n">
-        <v>8.029999999999999</v>
+        <v>8.3925</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.15</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4482</v>
+        <v>0.4223</v>
       </c>
       <c r="J282" t="n">
-        <v>9.8604</v>
+        <v>9.2906</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.86</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.15</v>
+        <v>-0.1698</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.3</v>
+        <v>-3.7356</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.78</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2315</v>
+        <v>-0.2509</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.093</v>
+        <v>-5.5198</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.57</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.428</v>
+        <v>-0.4408</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.416</v>
+        <v>-9.6976</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.48</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5115</v>
+        <v>-0.5195</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.253</v>
+        <v>-11.429</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.55</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1668</v>
+        <v>1.1387</v>
       </c>
       <c r="J287" t="n">
-        <v>25.6696</v>
+        <v>25.0514</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.53</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1427</v>
+        <v>1.1127</v>
       </c>
       <c r="J288" t="n">
-        <v>25.1394</v>
+        <v>24.4794</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.43</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0165</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="J289" t="n">
-        <v>22.363</v>
+        <v>21.3246</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.21</v>
       </c>
       <c r="I290" t="n">
-        <v>0.5481</v>
+        <v>0.542</v>
       </c>
       <c r="J290" t="n">
-        <v>12.0582</v>
+        <v>11.924</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>1.2</v>
       </c>
       <c r="I291" t="n">
-        <v>0.5235</v>
+        <v>0.52</v>
       </c>
       <c r="J291" t="n">
-        <v>11.517</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.39</v>
       </c>
       <c r="I292" t="n">
-        <v>0.7745</v>
+        <v>0.7388</v>
       </c>
       <c r="J292" t="n">
-        <v>19.3625</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.03</v>
       </c>
       <c r="I293" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="J293" t="n">
-        <v>2.3325</v>
+        <v>2.525</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.99</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0201</v>
+        <v>-0.0249</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.6225000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.82</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2179</v>
+        <v>-0.2317</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.4475</v>
+        <v>-5.7925</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3067</v>
+        <v>-0.3191</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.6675</v>
+        <v>-7.9775</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.59</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2815</v>
+        <v>1.2491</v>
       </c>
       <c r="J297" t="n">
-        <v>32.0375</v>
+        <v>31.2275</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.16</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4773</v>
+        <v>0.4667</v>
       </c>
       <c r="J298" t="n">
-        <v>11.9325</v>
+        <v>11.6675</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3999</v>
+        <v>0.3961</v>
       </c>
       <c r="J299" t="n">
-        <v>9.9975</v>
+        <v>9.9025</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.06</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2044</v>
+        <v>0.2137</v>
       </c>
       <c r="J300" t="n">
-        <v>5.11</v>
+        <v>5.3425</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0494</v>
+        <v>-0.9563</v>
       </c>
       <c r="J301" t="n">
-        <v>-26.235</v>
+        <v>-23.9075</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>2.38</v>
       </c>
       <c r="I302" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J302" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.78</v>
       </c>
       <c r="I303" t="n">
-        <v>1.3863</v>
+        <v>1.3825</v>
       </c>
       <c r="J303" t="n">
-        <v>23.5671</v>
+        <v>23.5025</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.62</v>
       </c>
       <c r="I304" t="n">
-        <v>1.2123</v>
+        <v>1.1955</v>
       </c>
       <c r="J304" t="n">
-        <v>20.6091</v>
+        <v>20.3235</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.51</v>
       </c>
       <c r="I305" t="n">
-        <v>1.0841</v>
+        <v>1.0562</v>
       </c>
       <c r="J305" t="n">
-        <v>18.4297</v>
+        <v>17.9554</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.38</v>
       </c>
       <c r="I306" t="n">
-        <v>0.87</v>
+        <v>0.8389</v>
       </c>
       <c r="J306" t="n">
-        <v>14.79</v>
+        <v>14.2613</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>0.92</v>
       </c>
       <c r="I307" t="n">
-        <v>0.0673</v>
+        <v>-0.0068</v>
       </c>
       <c r="J307" t="n">
-        <v>1.1441</v>
+        <v>-0.1156</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.42</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.5194</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="J308" t="n">
-        <v>-8.829800000000001</v>
+        <v>-9.0746</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.4</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.5387</v>
+        <v>-0.5516</v>
       </c>
       <c r="J309" t="n">
-        <v>-9.1579</v>
+        <v>-9.3772</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.4</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5387</v>
+        <v>-0.5516</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.1579</v>
+        <v>-9.3772</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.35</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5879</v>
+        <v>-0.5967</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.994300000000001</v>
+        <v>-10.1439</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.8</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4533</v>
+        <v>1.4453</v>
       </c>
       <c r="J312" t="n">
-        <v>31.9726</v>
+        <v>31.7966</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.62</v>
       </c>
       <c r="I313" t="n">
-        <v>1.2436</v>
+        <v>1.2224</v>
       </c>
       <c r="J313" t="n">
-        <v>27.3592</v>
+        <v>26.8928</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.44</v>
       </c>
       <c r="I314" t="n">
-        <v>1.0262</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="J314" t="n">
-        <v>22.5764</v>
+        <v>21.5908</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.27</v>
       </c>
       <c r="I315" t="n">
-        <v>0.6821</v>
+        <v>0.663</v>
       </c>
       <c r="J315" t="n">
-        <v>15.0062</v>
+        <v>14.586</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>1</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1003</v>
+        <v>-0.0698</v>
       </c>
       <c r="J316" t="n">
-        <v>-2.2066</v>
+        <v>-1.5356</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>0.97</v>
       </c>
       <c r="I317" t="n">
-        <v>0.0071</v>
+        <v>-0.0162</v>
       </c>
       <c r="J317" t="n">
-        <v>0.1562</v>
+        <v>-0.3564</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>0.75</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.2515</v>
+        <v>-0.2725</v>
       </c>
       <c r="J318" t="n">
-        <v>-5.533</v>
+        <v>-5.995</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.64</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3526</v>
+        <v>-0.3707</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.7572</v>
+        <v>-8.1554</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.59</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3992</v>
+        <v>-0.4152</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.782400000000001</v>
+        <v>-9.134399999999999</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.57</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4179</v>
+        <v>-0.4329</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.1938</v>
+        <v>-9.5238</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4574/event_4574_evp_summary.xlsx
+++ b/database/event/4574/event_4574_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.028</v>
+        <v>8.9529</v>
       </c>
       <c r="C2" t="n">
-        <v>3.122</v>
+        <v>3.096</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4855</v>
+        <v>3.4727</v>
       </c>
       <c r="E2" t="n">
-        <v>9.028</v>
+        <v>8.9529</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5329</v>
+        <v>3.4223</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4951</v>
+        <v>5.5306</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7623</v>
+        <v>6.4061</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6516</v>
+        <v>3.5968</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4951</v>
+        <v>5.5306</v>
       </c>
       <c r="K2" t="n">
         <v>122</v>
@@ -529,7 +529,7 @@
         <v>119</v>
       </c>
       <c r="M2" t="n">
-        <v>9.146699999999999</v>
+        <v>9.1274</v>
       </c>
       <c r="N2" t="n">
         <v>241</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6707</v>
+        <v>7.5396</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6526</v>
+        <v>2.6073</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8677</v>
+        <v>2.8289</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6707</v>
+        <v>7.5396</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3753</v>
+        <v>3.2914</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2954</v>
+        <v>4.2482</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2423</v>
+        <v>5.9147</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3708</v>
+        <v>3.3209</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2954</v>
+        <v>4.2482</v>
       </c>
       <c r="K3" t="n">
         <v>122</v>
@@ -575,7 +575,7 @@
         <v>119</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6662</v>
+        <v>7.5691</v>
       </c>
       <c r="N3" t="n">
         <v>241</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.5164</v>
+        <v>7.5222</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5993</v>
+        <v>2.6013</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7974</v>
+        <v>2.8209</v>
       </c>
       <c r="E4" t="n">
-        <v>7.5164</v>
+        <v>7.5222</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9068</v>
+        <v>2.9367</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6096</v>
+        <v>4.5855</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6964</v>
+        <v>4.5832</v>
       </c>
       <c r="I4" t="n">
-        <v>2.536</v>
+        <v>2.5733</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6096</v>
+        <v>4.5855</v>
       </c>
       <c r="K4" t="n">
         <v>122</v>
@@ -621,7 +621,7 @@
         <v>119</v>
       </c>
       <c r="M4" t="n">
-        <v>7.1456</v>
+        <v>7.158799999999999</v>
       </c>
       <c r="N4" t="n">
         <v>241</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5503</v>
+        <v>5.7645</v>
       </c>
       <c r="C5" t="n">
-        <v>1.9194</v>
+        <v>1.9934</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9024</v>
+        <v>2.0202</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5503</v>
+        <v>5.7645</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6572</v>
+        <v>1.7597</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8931</v>
+        <v>4.0048</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6572</v>
+        <v>1.7597</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8949</v>
+        <v>0.988</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8931</v>
+        <v>4.0048</v>
       </c>
       <c r="K5" t="n">
         <v>122</v>
@@ -667,7 +667,7 @@
         <v>119</v>
       </c>
       <c r="M5" t="n">
-        <v>4.788</v>
+        <v>4.992800000000001</v>
       </c>
       <c r="N5" t="n">
         <v>241</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6561</v>
+        <v>4.365</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6101</v>
+        <v>1.5095</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4953</v>
+        <v>1.3827</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6561</v>
+        <v>4.365</v>
       </c>
       <c r="F6" t="n">
-        <v>3.955</v>
+        <v>3.7329</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6321</v>
       </c>
       <c r="H6" t="n">
-        <v>8.1548</v>
+        <v>7.5721</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4035</v>
+        <v>4.2515</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6321</v>
       </c>
       <c r="K6" t="n">
         <v>210</v>
@@ -713,7 +713,7 @@
         <v>69</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1046</v>
+        <v>4.8836</v>
       </c>
       <c r="N6" t="n">
         <v>279</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5007</v>
+        <v>4.3455</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5564</v>
+        <v>1.5027</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4246</v>
+        <v>1.3738</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5007</v>
+        <v>4.3455</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6549</v>
+        <v>3.5639</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8458</v>
+        <v>0.7816</v>
       </c>
       <c r="H7" t="n">
-        <v>7.1647</v>
+        <v>6.9377</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8689</v>
+        <v>3.8953</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8458</v>
+        <v>0.7816</v>
       </c>
       <c r="K7" t="n">
         <v>122</v>
@@ -759,7 +759,7 @@
         <v>119</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7147</v>
+        <v>4.6769</v>
       </c>
       <c r="N7" t="n">
         <v>241</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1885</v>
+        <v>4.1568</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4484</v>
+        <v>1.4375</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2825</v>
+        <v>1.2878</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1885</v>
+        <v>4.1568</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8368</v>
+        <v>2.6347</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3517</v>
+        <v>1.5221</v>
       </c>
       <c r="H8" t="n">
-        <v>7.7649</v>
+        <v>3.4492</v>
       </c>
       <c r="I8" t="n">
-        <v>4.193</v>
+        <v>1.9366</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3517</v>
+        <v>1.5221</v>
       </c>
       <c r="K8" t="n">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="L8" t="n">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5447</v>
+        <v>3.4587</v>
       </c>
       <c r="N8" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1883</v>
+        <v>4.101</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4484</v>
+        <v>1.4182</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2824</v>
+        <v>1.2624</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1883</v>
+        <v>4.101</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6313</v>
+        <v>2.639</v>
       </c>
       <c r="G9" t="n">
-        <v>1.557</v>
+        <v>1.462</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7875</v>
+        <v>3.4652</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0452</v>
+        <v>1.9456</v>
       </c>
       <c r="J9" t="n">
-        <v>1.557</v>
+        <v>1.462</v>
       </c>
       <c r="K9" t="n">
         <v>111</v>
@@ -851,7 +851,7 @@
         <v>136</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6022</v>
+        <v>3.4076</v>
       </c>
       <c r="N9" t="n">
         <v>247</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0272</v>
+        <v>4.0016</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3927</v>
+        <v>1.3838</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2091</v>
+        <v>1.2171</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0272</v>
+        <v>4.0016</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5751</v>
+        <v>3.6855</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4522</v>
+        <v>0.3161</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6019</v>
+        <v>7.3944</v>
       </c>
       <c r="I10" t="n">
-        <v>1.945</v>
+        <v>4.1517</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4522</v>
+        <v>0.3161</v>
       </c>
       <c r="K10" t="n">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L10" t="n">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3972</v>
+        <v>4.4678</v>
       </c>
       <c r="N10" t="n">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0185</v>
+        <v>3.8875</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3896</v>
+        <v>1.3443</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2051</v>
+        <v>1.1652</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0185</v>
+        <v>3.8875</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8524</v>
+        <v>3.8282</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1661</v>
+        <v>0.0593</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8162</v>
+        <v>7.9303</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2207</v>
+        <v>4.4526</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1661</v>
+        <v>0.0593</v>
       </c>
       <c r="K11" t="n">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3868</v>
+        <v>4.511900000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>234</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.0082</v>
+        <v>3.8322</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3861</v>
+        <v>1.3252</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2004</v>
+        <v>1.14</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0082</v>
+        <v>3.8322</v>
       </c>
       <c r="F12" t="n">
-        <v>3.9282</v>
+        <v>3.7067</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08</v>
+        <v>0.1255</v>
       </c>
       <c r="H12" t="n">
-        <v>8.0664</v>
+        <v>7.4738</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3558</v>
+        <v>4.1963</v>
       </c>
       <c r="J12" t="n">
-        <v>0.08</v>
+        <v>0.1255</v>
       </c>
       <c r="K12" t="n">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="L12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4358</v>
+        <v>4.3218</v>
       </c>
       <c r="N12" t="n">
-        <v>279</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2109</v>
+        <v>3.321</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1104</v>
+        <v>1.1484</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8375</v>
+        <v>0.9071</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2109</v>
+        <v>3.321</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4048</v>
+        <v>2.4808</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8061</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.04</v>
+        <v>2.8712</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6416</v>
+        <v>1.6121</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8061</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1035,7 +1035,7 @@
         <v>136</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4477</v>
+        <v>2.4523</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1044,170 +1044,170 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4415</v>
+        <v>2.3381</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8085</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4872</v>
+        <v>0.4593</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4415</v>
+        <v>2.3381</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4415</v>
+        <v>2.089</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.2491</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6187</v>
+        <v>2.089</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6187</v>
+        <v>1.1729</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.2491</v>
       </c>
       <c r="K14" t="n">
-        <v>207</v>
+        <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6187</v>
+        <v>1.422</v>
       </c>
       <c r="N14" t="n">
-        <v>207</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4266</v>
+        <v>2.3301</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8391</v>
+        <v>0.8058</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4804</v>
+        <v>0.4557</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4266</v>
+        <v>2.3301</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1795</v>
+        <v>2.3301</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2471</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2969</v>
+        <v>2.3897</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2403</v>
+        <v>2.3897</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2471</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>111</v>
+        <v>207</v>
       </c>
       <c r="L15" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4874</v>
+        <v>2.3897</v>
       </c>
       <c r="N15" t="n">
-        <v>247</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1685</v>
+        <v>2.113</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7499</v>
+        <v>0.7307</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3629</v>
+        <v>0.3568</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1685</v>
+        <v>2.113</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1685</v>
+        <v>2.4474</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.3344</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1685</v>
+        <v>2.7458</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1685</v>
+        <v>1.5417</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.3344</v>
       </c>
       <c r="K16" t="n">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1685</v>
+        <v>1.2073</v>
       </c>
       <c r="N16" t="n">
-        <v>189</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1077</v>
+        <v>2.0783</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7289</v>
+        <v>0.7187</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3353</v>
+        <v>0.341</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1077</v>
+        <v>2.0783</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1077</v>
+        <v>2.0783</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1077</v>
+        <v>2.0783</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1077</v>
+        <v>2.0783</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1077</v>
+        <v>2.0783</v>
       </c>
       <c r="N17" t="n">
         <v>189</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0733</v>
+        <v>2.0394</v>
       </c>
       <c r="C18" t="n">
-        <v>0.717</v>
+        <v>0.7053</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3196</v>
+        <v>0.3233</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0733</v>
+        <v>2.0394</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0733</v>
+        <v>2.3862</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.3468</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0733</v>
+        <v>2.5161</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0733</v>
+        <v>1.4127</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.3468</v>
       </c>
       <c r="K18" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0733</v>
+        <v>1.0659</v>
       </c>
       <c r="N18" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.938</v>
+        <v>2.0055</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6702</v>
+        <v>0.6935</v>
       </c>
       <c r="D19" t="n">
-        <v>0.258</v>
+        <v>0.3078</v>
       </c>
       <c r="E19" t="n">
-        <v>1.938</v>
+        <v>2.0055</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3173</v>
+        <v>2.0055</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3793</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7515</v>
+        <v>2.0055</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4858</v>
+        <v>2.0055</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3793</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L19" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1065</v>
+        <v>2.0055</v>
       </c>
       <c r="N19" t="n">
-        <v>279</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9355</v>
+        <v>1.8529</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6693</v>
+        <v>0.6408</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2569</v>
+        <v>0.2383</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9355</v>
+        <v>1.8529</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2569</v>
+        <v>1.8529</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5523</v>
+        <v>1.8529</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3782</v>
+        <v>1.8529</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0568</v>
+        <v>1.8529</v>
       </c>
       <c r="N20" t="n">
-        <v>234</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8979</v>
+        <v>1.7429</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6563</v>
+        <v>0.6027</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2398</v>
+        <v>0.1882</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8979</v>
+        <v>1.7429</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8979</v>
+        <v>1.7429</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8979</v>
+        <v>1.7429</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8979</v>
+        <v>1.7429</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8979</v>
+        <v>1.7429</v>
       </c>
       <c r="N21" t="n">
         <v>189</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7225</v>
+        <v>1.6102</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5957</v>
+        <v>0.5568</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1599</v>
+        <v>0.1277</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7225</v>
+        <v>1.6102</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7225</v>
+        <v>2.3979</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.7877</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7225</v>
+        <v>2.5601</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7225</v>
+        <v>1.4374</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.7877</v>
       </c>
       <c r="K22" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7225</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5195</v>
+        <v>1.5265</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5255</v>
+        <v>0.5279</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0675</v>
+        <v>0.0896</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5195</v>
+        <v>1.5265</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3251</v>
+        <v>1.5265</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8056</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7773</v>
+        <v>1.5265</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4997</v>
+        <v>1.5265</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8056</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="L23" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6941000000000001</v>
+        <v>1.5265</v>
       </c>
       <c r="N23" t="n">
-        <v>234</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4556</v>
+        <v>1.5234</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5034</v>
+        <v>0.5268</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0384</v>
+        <v>0.0882</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4556</v>
+        <v>1.5234</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5518</v>
+        <v>2.5789</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0962</v>
+        <v>-1.0555</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5251</v>
+        <v>3.2395</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9035</v>
+        <v>1.8189</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0962</v>
+        <v>-1.0555</v>
       </c>
       <c r="K24" t="n">
         <v>111</v>
@@ -1541,7 +1541,7 @@
         <v>136</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8072999999999999</v>
+        <v>0.7633999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>247</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3602</v>
+        <v>1.4651</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4704</v>
+        <v>0.5067</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.005</v>
+        <v>0.0616</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3602</v>
+        <v>1.4651</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2162</v>
+        <v>2.3402</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.856</v>
+        <v>-0.8751</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4178</v>
+        <v>2.3435</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3056</v>
+        <v>1.3158</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.856</v>
+        <v>-0.8751</v>
       </c>
       <c r="K25" t="n">
         <v>210</v>
@@ -1587,7 +1587,7 @@
         <v>69</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4496000000000001</v>
+        <v>0.4407000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>279</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.998</v>
+        <v>0.9634</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3451</v>
+        <v>0.3332</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1699</v>
+        <v>-0.1669</v>
       </c>
       <c r="E26" t="n">
-        <v>0.998</v>
+        <v>0.9634</v>
       </c>
       <c r="F26" t="n">
-        <v>0.998</v>
+        <v>0.9634</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.998</v>
+        <v>0.9634</v>
       </c>
       <c r="I26" t="n">
-        <v>0.998</v>
+        <v>0.9634</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.998</v>
+        <v>0.9634</v>
       </c>
       <c r="N26" t="n">
         <v>104</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7315</v>
+        <v>0.6177</v>
       </c>
       <c r="C27" t="n">
-        <v>0.253</v>
+        <v>0.2136</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2912</v>
+        <v>-0.3244</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7315</v>
+        <v>0.6177</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7315</v>
+        <v>0.6177</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7315</v>
+        <v>0.6177</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7315</v>
+        <v>0.6177</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7315</v>
+        <v>0.6177</v>
       </c>
       <c r="N27" t="n">
         <v>189</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2244</v>
+        <v>0.2191</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0776</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5221</v>
+        <v>-0.506</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2244</v>
+        <v>0.2191</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2244</v>
+        <v>0.2191</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2244</v>
+        <v>0.2191</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2244</v>
+        <v>0.2191</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2244</v>
+        <v>0.2191</v>
       </c>
       <c r="N28" t="n">
         <v>104</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0536</v>
+        <v>-0.015</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0185</v>
+        <v>-0.0052</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5998</v>
+        <v>-0.6126</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0536</v>
+        <v>-0.015</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0536</v>
+        <v>-0.015</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0536</v>
+        <v>-0.015</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0536</v>
+        <v>-0.015</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0536</v>
+        <v>-0.015</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0056</v>
+        <v>-0.0542</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0019</v>
+        <v>-0.0187</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6268</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0056</v>
+        <v>-0.0542</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0056</v>
+        <v>-0.0542</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0056</v>
+        <v>-0.0542</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0056</v>
+        <v>-0.0542</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0056</v>
+        <v>-0.0542</v>
       </c>
       <c r="N30" t="n">
         <v>207</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.025</v>
+        <v>-0.0452</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6572</v>
+        <v>-0.6654</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1308</v>
       </c>
       <c r="N31" t="n">
         <v>207</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.226</v>
+        <v>-0.1825</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0631</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7271</v>
+        <v>-0.6889</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.226</v>
+        <v>-0.1825</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.226</v>
+        <v>-0.1825</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.226</v>
+        <v>-0.1825</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.226</v>
+        <v>-0.1825</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.226</v>
+        <v>-0.1825</v>
       </c>
       <c r="N32" t="n">
-        <v>104</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2594</v>
+        <v>-0.2727</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0897</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7423</v>
+        <v>-0.73</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2594</v>
+        <v>-0.2727</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2594</v>
+        <v>-0.2727</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2594</v>
+        <v>-0.2727</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2594</v>
+        <v>-0.2727</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2594</v>
+        <v>-0.2727</v>
       </c>
       <c r="N33" t="n">
-        <v>189</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3709</v>
+        <v>-0.31</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1283</v>
+        <v>-0.1072</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.793</v>
+        <v>-0.747</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3709</v>
+        <v>-0.31</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3709</v>
+        <v>-0.31</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3709</v>
+        <v>-0.31</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3709</v>
+        <v>-0.31</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3709</v>
+        <v>-0.31</v>
       </c>
       <c r="N34" t="n">
         <v>125</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5265</v>
+        <v>-0.5392</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1821</v>
+        <v>-0.1865</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8639</v>
+        <v>-0.8514</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5265</v>
+        <v>-0.5392</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5265</v>
+        <v>-0.5392</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5265</v>
+        <v>-0.5392</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5265</v>
+        <v>-0.5392</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5265</v>
+        <v>-0.5392</v>
       </c>
       <c r="N35" t="n">
         <v>125</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5308</v>
+        <v>-0.5575</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1836</v>
+        <v>-0.1928</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8658</v>
+        <v>-0.8598</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5308</v>
+        <v>-0.5575</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5308</v>
+        <v>-0.5575</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5308</v>
+        <v>-0.5575</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5308</v>
+        <v>-0.5575</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5308</v>
+        <v>-0.5575</v>
       </c>
       <c r="N36" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5698</v>
+        <v>-0.5581</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.197</v>
+        <v>-0.193</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.86</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5698</v>
+        <v>-0.5581</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5698</v>
+        <v>-0.5581</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5698</v>
+        <v>-0.5581</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5698</v>
+        <v>-0.5581</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5698</v>
+        <v>-0.5581</v>
       </c>
       <c r="N37" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.5803</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2007</v>
+        <v>-0.2125</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8884</v>
+        <v>-0.8857</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5803</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5803</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5803</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5803</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.5803</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>86</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9674</v>
+        <v>-0.9648</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3345</v>
+        <v>-0.3336</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0646</v>
+        <v>-1.0453</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9674</v>
+        <v>-0.9648</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9674</v>
+        <v>-0.9648</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9674</v>
+        <v>-0.9648</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9674</v>
+        <v>-0.9648</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9674</v>
+        <v>-0.9648</v>
       </c>
       <c r="N39" t="n">
         <v>39</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2667</v>
+        <v>-1.2249</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.438</v>
+        <v>-0.4236</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2008</v>
+        <v>-1.1638</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2667</v>
+        <v>-1.2249</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2667</v>
+        <v>-1.2249</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2667</v>
+        <v>-1.2249</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2667</v>
+        <v>-1.2249</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2667</v>
+        <v>-1.2249</v>
       </c>
       <c r="N40" t="n">
         <v>104</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8743</v>
+        <v>-1.6922</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6482</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4774</v>
+        <v>-1.3767</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8743</v>
+        <v>-1.6922</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.28</v>
+        <v>-1.1317</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.5605</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.28</v>
+        <v>-1.1317</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6912</v>
+        <v>-0.6354</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.5605</v>
       </c>
       <c r="K41" t="n">
         <v>182</v>
@@ -2323,7 +2323,7 @@
         <v>52</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2855</v>
+        <v>-1.1959</v>
       </c>
       <c r="N41" t="n">
         <v>234</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-3.2206</v>
+        <v>-3.1403</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.1137</v>
+        <v>-1.086</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.0903</v>
+        <v>-2.0363</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.2206</v>
+        <v>-3.1403</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.2206</v>
+        <v>-2.1403</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.2206</v>
+        <v>-2.1403</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.1991</v>
+        <v>-1.2017</v>
       </c>
       <c r="J42" t="n">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>69</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.1991</v>
+        <v>-2.2017</v>
       </c>
       <c r="N42" t="n">
         <v>279</v>
@@ -2475,10 +2475,10 @@
         <v>0.83</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1717</v>
+        <v>-0.1538</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.0906</v>
+        <v>-2.7684</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2262</v>
+        <v>-0.2111</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.0716</v>
+        <v>-3.7998</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3955</v>
+        <v>-0.3868</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.119</v>
+        <v>-6.9624</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.58</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4127</v>
+        <v>-0.4045</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.4286</v>
+        <v>-7.281</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.3</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6586</v>
+        <v>-0.6807</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.8548</v>
+        <v>-12.2526</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.94</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7158</v>
+        <v>1.7505</v>
       </c>
       <c r="J7" t="n">
-        <v>30.8844</v>
+        <v>31.509</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.93</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7043</v>
+        <v>1.7383</v>
       </c>
       <c r="J8" t="n">
-        <v>30.6774</v>
+        <v>31.2894</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.53</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1213</v>
+        <v>1.1424</v>
       </c>
       <c r="J9" t="n">
-        <v>20.1834</v>
+        <v>20.5632</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.46</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9981</v>
+        <v>1.0069</v>
       </c>
       <c r="J10" t="n">
-        <v>17.9658</v>
+        <v>18.1242</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.34</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7739</v>
+        <v>0.7623</v>
       </c>
       <c r="J11" t="n">
-        <v>13.9302</v>
+        <v>13.7214</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>0.86</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1208</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2952</v>
+        <v>-1.8278</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.62</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3726</v>
+        <v>-0.3653</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.0794</v>
+        <v>-6.9407</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.58</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4077</v>
+        <v>-0.4015</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.7463</v>
+        <v>-7.6285</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.57</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4159</v>
+        <v>-0.4098</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.9021</v>
+        <v>-7.7862</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.22</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.724</v>
+        <v>-0.759</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.756</v>
+        <v>-14.421</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>2.02</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8147</v>
+        <v>1.8563</v>
       </c>
       <c r="J17" t="n">
-        <v>34.4793</v>
+        <v>35.2697</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5395</v>
+        <v>1.5721</v>
       </c>
       <c r="J18" t="n">
-        <v>29.2505</v>
+        <v>29.8699</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.73</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4522</v>
+        <v>1.4917</v>
       </c>
       <c r="J19" t="n">
-        <v>27.5918</v>
+        <v>28.3423</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6403</v>
+        <v>0.6187</v>
       </c>
       <c r="J20" t="n">
-        <v>12.1657</v>
+        <v>11.7553</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>1.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3521</v>
+        <v>0.3172</v>
       </c>
       <c r="J21" t="n">
-        <v>6.6899</v>
+        <v>6.0268</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.18</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3883</v>
+        <v>0.333</v>
       </c>
       <c r="J22" t="n">
-        <v>11.649</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3537</v>
+        <v>0.3003</v>
       </c>
       <c r="J23" t="n">
-        <v>10.611</v>
+        <v>9.009</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3537</v>
+        <v>0.3003</v>
       </c>
       <c r="J24" t="n">
-        <v>10.611</v>
+        <v>9.009</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1422</v>
+        <v>0.1107</v>
       </c>
       <c r="J25" t="n">
-        <v>4.266</v>
+        <v>3.321</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.72</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3338</v>
+        <v>-0.3185</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.014</v>
+        <v>-9.555</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.44</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0513</v>
+        <v>1.049</v>
       </c>
       <c r="J27" t="n">
-        <v>31.539</v>
+        <v>31.47</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5572</v>
+        <v>0.5191</v>
       </c>
       <c r="J28" t="n">
-        <v>16.716</v>
+        <v>15.573</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4895</v>
+        <v>0.4505</v>
       </c>
       <c r="J29" t="n">
-        <v>14.685</v>
+        <v>13.515</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0189</v>
+        <v>-0.014</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.78</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6565</v>
+        <v>-0.6226</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.695</v>
+        <v>-18.678</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.775</v>
+        <v>0.7595</v>
       </c>
       <c r="J32" t="n">
-        <v>20.925</v>
+        <v>20.5065</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.31</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6869</v>
+        <v>0.6732</v>
       </c>
       <c r="J33" t="n">
-        <v>18.5463</v>
+        <v>18.1764</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6266</v>
+        <v>0.6152</v>
       </c>
       <c r="J34" t="n">
-        <v>16.9182</v>
+        <v>16.6104</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.11</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3369</v>
+        <v>0.3034</v>
       </c>
       <c r="J35" t="n">
-        <v>9.096299999999999</v>
+        <v>8.191800000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.91</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3521</v>
+        <v>-0.3112</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.5067</v>
+        <v>-8.4024</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4548</v>
+        <v>0.4038</v>
       </c>
       <c r="J37" t="n">
-        <v>12.2796</v>
+        <v>10.9026</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3917</v>
+        <v>0.336</v>
       </c>
       <c r="J38" t="n">
-        <v>10.5759</v>
+        <v>9.071999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1312</v>
+        <v>0.099</v>
       </c>
       <c r="J39" t="n">
-        <v>3.5424</v>
+        <v>2.673</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2485</v>
+        <v>-0.2285</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.7095</v>
+        <v>-6.1695</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4598</v>
+        <v>-0.4557</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.4146</v>
+        <v>-12.3039</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.63</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0961</v>
+        <v>1.0878</v>
       </c>
       <c r="J42" t="n">
-        <v>27.4025</v>
+        <v>27.195</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8209</v>
+        <v>0.8097</v>
       </c>
       <c r="J43" t="n">
-        <v>20.5225</v>
+        <v>20.2425</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.41</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8075</v>
+        <v>0.7965</v>
       </c>
       <c r="J44" t="n">
-        <v>20.1875</v>
+        <v>19.9125</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.38</v>
       </c>
       <c r="I45" t="n">
-        <v>0.767</v>
+        <v>0.7569</v>
       </c>
       <c r="J45" t="n">
-        <v>19.175</v>
+        <v>18.9225</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0394</v>
+        <v>0.0213</v>
       </c>
       <c r="J46" t="n">
-        <v>0.985</v>
+        <v>0.5325</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>0.91</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1031</v>
+        <v>-0.0877</v>
       </c>
       <c r="J47" t="n">
-        <v>-2.5775</v>
+        <v>-2.1925</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.8</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2256</v>
+        <v>-0.2105</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.64</v>
+        <v>-5.2625</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3458</v>
+        <v>-0.332</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.645</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.67</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3458</v>
+        <v>-0.332</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.645</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4526</v>
+        <v>-0.4458</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.315</v>
+        <v>-11.145</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5845</v>
       </c>
       <c r="J52" t="n">
-        <v>13.6475</v>
+        <v>14.6125</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>0.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1584</v>
+        <v>-0.1411</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.96</v>
+        <v>-3.5275</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.72</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3153</v>
+        <v>-0.2981</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.8825</v>
+        <v>-7.4525</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3522</v>
+        <v>-0.3371</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.805</v>
+        <v>-8.4275</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.65</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3795</v>
+        <v>-0.3664</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.487500000000001</v>
+        <v>-9.16</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.71</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7289</v>
+        <v>0.6823</v>
       </c>
       <c r="J57" t="n">
-        <v>18.2225</v>
+        <v>17.0575</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5068</v>
+        <v>0.4616</v>
       </c>
       <c r="J58" t="n">
-        <v>12.67</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0922</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>2.305</v>
+        <v>1.7125</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0407</v>
+        <v>-0.0314</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.0175</v>
+        <v>-0.785</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1864</v>
+        <v>-0.1668</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.66</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0158</v>
+        <v>1.0042</v>
       </c>
       <c r="J62" t="n">
-        <v>21.3318</v>
+        <v>21.0882</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9495</v>
+        <v>0.9366</v>
       </c>
       <c r="J63" t="n">
-        <v>19.9395</v>
+        <v>19.6686</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5857</v>
+        <v>0.5805</v>
       </c>
       <c r="J64" t="n">
-        <v>12.2997</v>
+        <v>12.1905</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>1.25</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5857</v>
+        <v>0.5805</v>
       </c>
       <c r="J65" t="n">
-        <v>12.2997</v>
+        <v>12.1905</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.99</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1123</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.3583</v>
+        <v>-1.9488</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.11</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3414</v>
+        <v>0.2981</v>
       </c>
       <c r="J67" t="n">
-        <v>7.1694</v>
+        <v>6.2601</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>0.84</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1915</v>
+        <v>-0.1754</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.0215</v>
+        <v>-3.6834</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>0.73</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2967</v>
+        <v>-0.2803</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.2307</v>
+        <v>-5.8863</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.66</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3606</v>
+        <v>-0.3465</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.5726</v>
+        <v>-7.2765</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.51</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4936</v>
+        <v>-0.4917</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.3656</v>
+        <v>-10.3257</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0382</v>
+        <v>1.029</v>
       </c>
       <c r="J72" t="n">
-        <v>23.8786</v>
+        <v>23.667</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.56</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9998</v>
+        <v>0.9899</v>
       </c>
       <c r="J73" t="n">
-        <v>22.9954</v>
+        <v>22.7677</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9869</v>
+        <v>0.9769</v>
       </c>
       <c r="J74" t="n">
-        <v>22.6987</v>
+        <v>22.4687</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.45</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8568</v>
+        <v>0.8467</v>
       </c>
       <c r="J75" t="n">
-        <v>19.7064</v>
+        <v>19.4741</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3024</v>
+        <v>-0.2696</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.9552</v>
+        <v>-6.2008</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>0.85</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1471</v>
+        <v>-0.1276</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.3833</v>
+        <v>-2.9348</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>0.85</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1471</v>
+        <v>-0.1276</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.3833</v>
+        <v>-2.9348</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.65</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3522</v>
+        <v>-0.3427</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.1006</v>
+        <v>-7.8821</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.38</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5876</v>
+        <v>-0.5971</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.5148</v>
+        <v>-13.7333</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.33</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.6485</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.5268</v>
+        <v>-14.9155</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2273</v>
+        <v>1.2433</v>
       </c>
       <c r="J82" t="n">
-        <v>28.2279</v>
+        <v>28.5959</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.45</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0106</v>
+        <v>1.0122</v>
       </c>
       <c r="J83" t="n">
-        <v>23.2438</v>
+        <v>23.2806</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.34</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8135</v>
+        <v>0.7954</v>
       </c>
       <c r="J84" t="n">
-        <v>18.7105</v>
+        <v>18.2942</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.317</v>
+        <v>0.2851</v>
       </c>
       <c r="J85" t="n">
-        <v>7.291</v>
+        <v>6.5573</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>1.08</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2372</v>
+        <v>0.2069</v>
       </c>
       <c r="J86" t="n">
-        <v>5.4556</v>
+        <v>4.7587</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.16</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4061</v>
+        <v>0.3539</v>
       </c>
       <c r="J87" t="n">
-        <v>9.340299999999999</v>
+        <v>8.139699999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.07</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2257</v>
+        <v>0.1834</v>
       </c>
       <c r="J88" t="n">
-        <v>5.1911</v>
+        <v>4.2182</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2286</v>
+        <v>-0.2097</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.2578</v>
+        <v>-4.8231</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.68</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3516</v>
+        <v>-0.3365</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.0868</v>
+        <v>-7.7395</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4762</v>
+        <v>-0.4729</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.9526</v>
+        <v>-10.8767</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.57</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7976</v>
+        <v>0.8696</v>
       </c>
       <c r="J92" t="n">
-        <v>22.3328</v>
+        <v>24.3488</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>0.87</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1761</v>
+        <v>-0.1561</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.9308</v>
+        <v>-4.3708</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1868</v>
+        <v>-0.1665</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.2304</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2871</v>
+        <v>-0.2684</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.0388</v>
+        <v>-7.5152</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.71</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3342</v>
+        <v>-0.3182</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.3576</v>
+        <v>-8.909599999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.34</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4701</v>
+        <v>0.4029</v>
       </c>
       <c r="J97" t="n">
-        <v>13.1628</v>
+        <v>11.2812</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.17</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2697</v>
+        <v>0.2182</v>
       </c>
       <c r="J98" t="n">
-        <v>7.5516</v>
+        <v>6.1096</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.15</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2441</v>
+        <v>0.1957</v>
       </c>
       <c r="J99" t="n">
-        <v>6.8348</v>
+        <v>5.4796</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1181</v>
+        <v>0.089</v>
       </c>
       <c r="J100" t="n">
-        <v>3.3068</v>
+        <v>2.492</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2516</v>
+        <v>-0.2322</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.0448</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>1.031</v>
+        <v>1.0334</v>
       </c>
       <c r="J102" t="n">
-        <v>25.775</v>
+        <v>25.835</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7716</v>
+        <v>0.7458</v>
       </c>
       <c r="J103" t="n">
-        <v>19.29</v>
+        <v>18.645</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.27</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6904</v>
+        <v>0.6606</v>
       </c>
       <c r="J104" t="n">
-        <v>17.26</v>
+        <v>16.515</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3089</v>
+        <v>0.2764</v>
       </c>
       <c r="J105" t="n">
-        <v>7.7225</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3546</v>
+        <v>-0.314</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.865</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4517</v>
+        <v>0.3949</v>
       </c>
       <c r="J107" t="n">
-        <v>11.2925</v>
+        <v>9.8725</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.03</v>
       </c>
       <c r="I108" t="n">
-        <v>0.111</v>
+        <v>0.082</v>
       </c>
       <c r="J108" t="n">
-        <v>2.775</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0206</v>
+        <v>-0.0153</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.515</v>
+        <v>-0.3825</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.85</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1953</v>
+        <v>-0.1752</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.8825</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.59</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4401</v>
+        <v>-0.4334</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.0025</v>
+        <v>-10.835</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4338</v>
+        <v>0.383</v>
       </c>
       <c r="J112" t="n">
-        <v>11.7126</v>
+        <v>10.341</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.03</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1371</v>
+        <v>0.1068</v>
       </c>
       <c r="J113" t="n">
-        <v>3.7017</v>
+        <v>2.8836</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0839</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.2653</v>
+        <v>-1.917</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.65</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3763</v>
+        <v>-0.3629</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.1601</v>
+        <v>-9.798299999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.35</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6355</v>
+        <v>-0.6566</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.1585</v>
+        <v>-17.7282</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1092</v>
+        <v>1.1219</v>
       </c>
       <c r="J117" t="n">
-        <v>29.9484</v>
+        <v>30.2913</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.49</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0689</v>
+        <v>1.0786</v>
       </c>
       <c r="J118" t="n">
-        <v>28.8603</v>
+        <v>29.1222</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9439</v>
+        <v>0.9358</v>
       </c>
       <c r="J119" t="n">
-        <v>25.4853</v>
+        <v>25.2666</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>1.29</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7178</v>
+        <v>0.6949</v>
       </c>
       <c r="J120" t="n">
-        <v>19.3806</v>
+        <v>18.7623</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4516</v>
+        <v>-0.4143</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.1932</v>
+        <v>-11.1861</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.26</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3829</v>
+        <v>0.3206</v>
       </c>
       <c r="J122" t="n">
-        <v>10.7212</v>
+        <v>8.976800000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2469</v>
+        <v>0.1975</v>
       </c>
       <c r="J123" t="n">
-        <v>6.9132</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2205</v>
+        <v>0.1744</v>
       </c>
       <c r="J124" t="n">
-        <v>6.174</v>
+        <v>4.8832</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="J125" t="n">
-        <v>2.4332</v>
+        <v>1.7752</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2493</v>
+        <v>-0.2296</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.9804</v>
+        <v>-6.4288</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5327</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J127" t="n">
-        <v>14.9156</v>
+        <v>15.3132</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1778</v>
+        <v>0.1616</v>
       </c>
       <c r="J128" t="n">
-        <v>4.9784</v>
+        <v>4.5248</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.04</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0945</v>
+        <v>0.0809</v>
       </c>
       <c r="J129" t="n">
-        <v>2.646</v>
+        <v>2.2652</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1614</v>
+        <v>-0.1411</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.5192</v>
+        <v>-3.9508</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.8</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2556</v>
+        <v>-0.236</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.1568</v>
+        <v>-6.608</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.09</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2726</v>
+        <v>0.227</v>
       </c>
       <c r="J132" t="n">
-        <v>5.9972</v>
+        <v>4.994</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0984</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.1648</v>
+        <v>-1.859</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.89</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1457</v>
+        <v>-0.1294</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.2054</v>
+        <v>-2.8468</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.86</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1781</v>
+        <v>-0.1606</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.9182</v>
+        <v>-3.5332</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5693</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.5246</v>
+        <v>-12.7402</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.74</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3949</v>
+        <v>1.4197</v>
       </c>
       <c r="J137" t="n">
-        <v>30.6878</v>
+        <v>31.2334</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.28</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6989</v>
+        <v>0.6748</v>
       </c>
       <c r="J138" t="n">
-        <v>15.3758</v>
+        <v>14.8456</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.21</v>
       </c>
       <c r="I139" t="n">
-        <v>0.553</v>
+        <v>0.5238</v>
       </c>
       <c r="J139" t="n">
-        <v>12.166</v>
+        <v>11.5236</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>1.18</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4863</v>
+        <v>0.4555</v>
       </c>
       <c r="J140" t="n">
-        <v>10.6986</v>
+        <v>10.021</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3928</v>
+        <v>0.3608</v>
       </c>
       <c r="J141" t="n">
-        <v>8.6416</v>
+        <v>7.9376</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.12</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3016</v>
+        <v>0.2508</v>
       </c>
       <c r="J142" t="n">
-        <v>8.444800000000001</v>
+        <v>7.0224</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0805</v>
+        <v>0.0572</v>
       </c>
       <c r="J143" t="n">
-        <v>2.254</v>
+        <v>1.6016</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0499</v>
+        <v>0.0334</v>
       </c>
       <c r="J144" t="n">
-        <v>1.3972</v>
+        <v>0.9352</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.99</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0222</v>
+        <v>-0.0165</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.6216</v>
+        <v>-0.462</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4242</v>
+        <v>-0.4159</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.8776</v>
+        <v>-11.6452</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9564</v>
+        <v>0.9474</v>
       </c>
       <c r="J147" t="n">
-        <v>26.7792</v>
+        <v>26.5272</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.32</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7844</v>
+        <v>0.7611</v>
       </c>
       <c r="J148" t="n">
-        <v>21.9632</v>
+        <v>21.3108</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.25</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6446</v>
+        <v>0.6153</v>
       </c>
       <c r="J149" t="n">
-        <v>18.0488</v>
+        <v>17.2284</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.16</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4499</v>
+        <v>0.417</v>
       </c>
       <c r="J150" t="n">
-        <v>12.5972</v>
+        <v>11.676</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>1.1</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3024</v>
+        <v>0.2705</v>
       </c>
       <c r="J151" t="n">
-        <v>8.4672</v>
+        <v>7.574</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3667</v>
+        <v>0.3119</v>
       </c>
       <c r="J152" t="n">
-        <v>11.001</v>
+        <v>9.356999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.01</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0446</v>
+        <v>0.03</v>
       </c>
       <c r="J153" t="n">
-        <v>1.338</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.042</v>
+        <v>-0.0321</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.26</v>
+        <v>-0.963</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.9</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1459</v>
+        <v>-0.1264</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.377</v>
+        <v>-3.792</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1572</v>
+        <v>-0.1373</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.716</v>
+        <v>-4.119</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8484</v>
+        <v>0.826</v>
       </c>
       <c r="J157" t="n">
-        <v>25.452</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4866</v>
+        <v>0.4486</v>
       </c>
       <c r="J158" t="n">
-        <v>14.598</v>
+        <v>13.458</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4638</v>
+        <v>0.4258</v>
       </c>
       <c r="J159" t="n">
-        <v>13.914</v>
+        <v>12.774</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.294</v>
+        <v>0.2599</v>
       </c>
       <c r="J160" t="n">
-        <v>8.82</v>
+        <v>7.797</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3139</v>
+        <v>-0.2728</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.417</v>
+        <v>-8.183999999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7911</v>
+        <v>0.7641</v>
       </c>
       <c r="J162" t="n">
-        <v>22.1508</v>
+        <v>21.3948</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6223</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>17.4244</v>
+        <v>16.4136</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5786</v>
+        <v>0.5412</v>
       </c>
       <c r="J164" t="n">
-        <v>16.2008</v>
+        <v>15.1536</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1912</v>
+        <v>-0.1566</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.3536</v>
+        <v>-4.3848</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.9</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3659</v>
+        <v>-0.3236</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.2452</v>
+        <v>-9.0608</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.43</v>
       </c>
       <c r="I167" t="n">
-        <v>0.792</v>
+        <v>0.7395</v>
       </c>
       <c r="J167" t="n">
-        <v>22.176</v>
+        <v>20.706</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2307</v>
+        <v>0.1865</v>
       </c>
       <c r="J168" t="n">
-        <v>6.4596</v>
+        <v>5.222</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.86</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.192</v>
+        <v>-0.1713</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.376</v>
+        <v>-4.7964</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.213</v>
+        <v>-0.1924</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.964</v>
+        <v>-5.3872</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.84</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.213</v>
+        <v>-0.1924</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.964</v>
+        <v>-5.3872</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.64</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2586</v>
+        <v>1.2762</v>
       </c>
       <c r="J172" t="n">
-        <v>28.9478</v>
+        <v>29.3526</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.36</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8472</v>
+        <v>0.8333</v>
       </c>
       <c r="J173" t="n">
-        <v>19.4856</v>
+        <v>19.1659</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.29</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7129</v>
+        <v>0.6917</v>
       </c>
       <c r="J174" t="n">
-        <v>16.3967</v>
+        <v>15.9091</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.28</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6928</v>
+        <v>0.6706</v>
       </c>
       <c r="J175" t="n">
-        <v>15.9344</v>
+        <v>15.4238</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>1.22</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5676</v>
+        <v>0.5401</v>
       </c>
       <c r="J176" t="n">
-        <v>13.0548</v>
+        <v>12.4223</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.04</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1867</v>
+        <v>0.1553</v>
       </c>
       <c r="J177" t="n">
-        <v>4.2941</v>
+        <v>3.5719</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.91</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1113</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.5599</v>
+        <v>-2.2218</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.76</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2687</v>
+        <v>-0.2524</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.1801</v>
+        <v>-5.8052</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.67</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3506</v>
+        <v>-0.3361</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.063800000000001</v>
+        <v>-7.7303</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.43</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5619</v>
+        <v>-0.5694</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.9237</v>
+        <v>-13.0962</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.36</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4804</v>
+        <v>0.4133</v>
       </c>
       <c r="J182" t="n">
-        <v>12.9708</v>
+        <v>11.1591</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.3</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4146</v>
+        <v>0.3514</v>
       </c>
       <c r="J183" t="n">
-        <v>11.1942</v>
+        <v>9.4878</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2762</v>
+        <v>0.2259</v>
       </c>
       <c r="J184" t="n">
-        <v>7.4574</v>
+        <v>6.0993</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.15</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2389</v>
+        <v>0.1932</v>
       </c>
       <c r="J185" t="n">
-        <v>6.4503</v>
+        <v>5.2164</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.114</v>
+        <v>-0.0963</v>
       </c>
       <c r="J186" t="n">
-        <v>-3.078</v>
+        <v>-2.6001</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8137</v>
+        <v>0.888</v>
       </c>
       <c r="J187" t="n">
-        <v>21.9699</v>
+        <v>23.976</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3451</v>
+        <v>0.3368</v>
       </c>
       <c r="J188" t="n">
-        <v>9.3177</v>
+        <v>9.0936</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.85</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1989</v>
+        <v>-0.1784</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.3703</v>
+        <v>-4.8168</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.77</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2792</v>
+        <v>-0.2602</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.5384</v>
+        <v>-7.0254</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.45</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5628</v>
+        <v>-0.5735</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.1956</v>
+        <v>-15.4845</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.31</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6706</v>
+        <v>0.6241</v>
       </c>
       <c r="J192" t="n">
-        <v>16.765</v>
+        <v>15.6025</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.89</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1461</v>
+        <v>-0.1297</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.6525</v>
+        <v>-3.2425</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.8</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2376</v>
+        <v>-0.2189</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.94</v>
+        <v>-5.4725</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3689</v>
+        <v>-0.355</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.2225</v>
+        <v>-8.875</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4579</v>
+        <v>-0.4524</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.4475</v>
+        <v>-11.31</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9908</v>
+        <v>0.9872</v>
       </c>
       <c r="J197" t="n">
-        <v>24.77</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.23</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6039</v>
+        <v>0.5734</v>
       </c>
       <c r="J198" t="n">
-        <v>15.0975</v>
+        <v>14.335</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.22</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5829</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>14.5725</v>
+        <v>13.7975</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.2</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5399</v>
+        <v>0.5081</v>
       </c>
       <c r="J200" t="n">
-        <v>13.4975</v>
+        <v>12.7025</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>1.16</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4499</v>
+        <v>0.417</v>
       </c>
       <c r="J201" t="n">
-        <v>11.2475</v>
+        <v>10.425</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.51</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9275</v>
+        <v>0.8889</v>
       </c>
       <c r="J202" t="n">
-        <v>31.535</v>
+        <v>30.2226</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.96</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0702</v>
+        <v>-0.0569</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.3868</v>
+        <v>-1.9346</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.92</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1206</v>
+        <v>-0.1028</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.1004</v>
+        <v>-3.4952</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.78</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2686</v>
+        <v>-0.2491</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.132400000000001</v>
+        <v>-8.4694</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3986</v>
+        <v>-0.3879</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.5524</v>
+        <v>-13.1886</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3676</v>
+        <v>1.3978</v>
       </c>
       <c r="J207" t="n">
-        <v>46.4984</v>
+        <v>47.5252</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.37</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9233</v>
+        <v>0.9081</v>
       </c>
       <c r="J208" t="n">
-        <v>31.3922</v>
+        <v>30.8754</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.85</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4863</v>
+        <v>-0.4443</v>
       </c>
       <c r="J209" t="n">
-        <v>-16.5342</v>
+        <v>-15.1062</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.78</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6505</v>
+        <v>-0.6155</v>
       </c>
       <c r="J210" t="n">
-        <v>-22.117</v>
+        <v>-20.927</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.76</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6953</v>
+        <v>-0.6633</v>
       </c>
       <c r="J211" t="n">
-        <v>-23.6402</v>
+        <v>-22.5522</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.23</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3804</v>
+        <v>0.3754</v>
       </c>
       <c r="J212" t="n">
-        <v>11.0316</v>
+        <v>10.8866</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.22</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3673</v>
+        <v>0.361</v>
       </c>
       <c r="J213" t="n">
-        <v>10.6517</v>
+        <v>10.469</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.92</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1231</v>
+        <v>-0.1047</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.5699</v>
+        <v>-3.0363</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2009</v>
+        <v>-0.1803</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.8261</v>
+        <v>-5.2287</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3004</v>
+        <v>-0.2825</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.711600000000001</v>
+        <v>-8.192500000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.33</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4629</v>
+        <v>0.396</v>
       </c>
       <c r="J217" t="n">
-        <v>13.4241</v>
+        <v>11.484</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2465</v>
+        <v>0.1972</v>
       </c>
       <c r="J218" t="n">
-        <v>7.1485</v>
+        <v>5.7188</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1356</v>
+        <v>0.1028</v>
       </c>
       <c r="J219" t="n">
-        <v>3.9324</v>
+        <v>2.9812</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.031</v>
+        <v>-0.0222</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.899</v>
+        <v>-0.6438</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1873</v>
+        <v>-0.1668</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.4317</v>
+        <v>-4.8372</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.19</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.503</v>
       </c>
       <c r="J222" t="n">
-        <v>15.7412</v>
+        <v>14.587</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.16</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4734</v>
+        <v>0.4327</v>
       </c>
       <c r="J223" t="n">
-        <v>13.7286</v>
+        <v>12.5483</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3769</v>
+        <v>0.3371</v>
       </c>
       <c r="J224" t="n">
-        <v>10.9301</v>
+        <v>9.7759</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1496</v>
+        <v>-0.1188</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.3384</v>
+        <v>-3.4452</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1833</v>
+        <v>-0.1492</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.3157</v>
+        <v>-4.3268</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.16</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3604</v>
+        <v>0.306</v>
       </c>
       <c r="J227" t="n">
-        <v>10.4516</v>
+        <v>8.874000000000001</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2876</v>
+        <v>0.2383</v>
       </c>
       <c r="J228" t="n">
-        <v>8.340400000000001</v>
+        <v>6.9107</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2297</v>
+        <v>0.1858</v>
       </c>
       <c r="J229" t="n">
-        <v>6.6613</v>
+        <v>5.3882</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0592</v>
       </c>
       <c r="J230" t="n">
-        <v>-2.1431</v>
+        <v>-1.7168</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.76</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.293</v>
+        <v>-0.2748</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.497</v>
+        <v>-7.9692</v>
       </c>
     </row>
     <row r="232">
@@ -11715,10 +11715,10 @@
         <v>1.34</v>
       </c>
       <c r="I233" t="n">
-        <v>0.833</v>
+        <v>0.8109</v>
       </c>
       <c r="J233" t="n">
-        <v>20.825</v>
+        <v>20.2725</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.13</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3858</v>
+        <v>0.3516</v>
       </c>
       <c r="J234" t="n">
-        <v>9.645</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.09</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2838</v>
+        <v>0.2519</v>
       </c>
       <c r="J235" t="n">
-        <v>7.095</v>
+        <v>6.2975</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0336</v>
+        <v>-0.028</v>
       </c>
       <c r="J236" t="n">
-        <v>-0.84</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.34</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6768</v>
+        <v>0.622</v>
       </c>
       <c r="J237" t="n">
-        <v>16.92</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.09</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2429</v>
+        <v>0.1969</v>
       </c>
       <c r="J238" t="n">
-        <v>6.0725</v>
+        <v>4.9225</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1426</v>
+        <v>-0.1238</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.565</v>
+        <v>-3.095</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2769</v>
+        <v>-0.2578</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.9225</v>
+        <v>-6.445</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3974</v>
+        <v>-0.3864</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.935</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4492</v>
+        <v>0.4018</v>
       </c>
       <c r="J242" t="n">
-        <v>10.3316</v>
+        <v>9.241400000000001</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>0.84</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1942</v>
+        <v>-0.1776</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.4666</v>
+        <v>-4.0848</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.73</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.299</v>
+        <v>-0.2821</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.877</v>
+        <v>-6.4883</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.61</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4081</v>
+        <v>-0.3972</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.3863</v>
+        <v>-9.1356</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.61</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4081</v>
+        <v>-0.3972</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.3863</v>
+        <v>-9.1356</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2158</v>
+        <v>1.2313</v>
       </c>
       <c r="J247" t="n">
-        <v>27.9634</v>
+        <v>28.3199</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.47</v>
       </c>
       <c r="I248" t="n">
-        <v>1.0419</v>
+        <v>1.048</v>
       </c>
       <c r="J248" t="n">
-        <v>23.9637</v>
+        <v>24.104</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>1.41</v>
       </c>
       <c r="I249" t="n">
-        <v>0.9452</v>
+        <v>0.9369</v>
       </c>
       <c r="J249" t="n">
-        <v>21.7396</v>
+        <v>21.5487</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>1.29</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7187</v>
+        <v>0.6954</v>
       </c>
       <c r="J250" t="n">
-        <v>16.5301</v>
+        <v>15.9942</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6878</v>
+        <v>-0.6613</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.8194</v>
+        <v>-15.2099</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.7</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1124</v>
+        <v>1.1005</v>
       </c>
       <c r="J252" t="n">
-        <v>33.372</v>
+        <v>33.015</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1626</v>
+        <v>0.1287</v>
       </c>
       <c r="J253" t="n">
-        <v>4.878</v>
+        <v>3.861</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1047</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J254" t="n">
-        <v>-3.141</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1047</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.141</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3444</v>
+        <v>-0.33</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.332</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4351</v>
+        <v>0.3929</v>
       </c>
       <c r="J257" t="n">
-        <v>13.053</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.08</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2804</v>
+        <v>0.2421</v>
       </c>
       <c r="J258" t="n">
-        <v>8.412000000000001</v>
+        <v>7.263</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.04</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1635</v>
+        <v>0.1341</v>
       </c>
       <c r="J259" t="n">
-        <v>4.905</v>
+        <v>4.023</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>1.02</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0954</v>
+        <v>0.0746</v>
       </c>
       <c r="J260" t="n">
-        <v>2.862</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.9</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3492</v>
+        <v>-0.3067</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.476</v>
+        <v>-9.201000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.21</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4721</v>
+        <v>0.4153</v>
       </c>
       <c r="J262" t="n">
-        <v>14.163</v>
+        <v>12.459</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>0.97</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0532</v>
+        <v>-0.0428</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.596</v>
+        <v>-1.284</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0555</v>
       </c>
       <c r="J264" t="n">
-        <v>-2.028</v>
+        <v>-1.665</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.094</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.82</v>
+        <v>-2.376</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.53</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4913</v>
+        <v>-0.4907</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.739</v>
+        <v>-14.721</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.5</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1069</v>
+        <v>1.1185</v>
       </c>
       <c r="J267" t="n">
-        <v>33.207</v>
+        <v>33.555</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.18</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5032</v>
+        <v>0.468</v>
       </c>
       <c r="J268" t="n">
-        <v>15.096</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>1.16</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4584</v>
+        <v>0.4231</v>
       </c>
       <c r="J269" t="n">
-        <v>13.752</v>
+        <v>12.693</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>1.15</v>
       </c>
       <c r="I270" t="n">
-        <v>0.4352</v>
+        <v>0.4001</v>
       </c>
       <c r="J270" t="n">
-        <v>13.056</v>
+        <v>12.003</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.95</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2352</v>
+        <v>-0.1984</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.056</v>
+        <v>-5.952</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.47</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9408</v>
+        <v>0.9238</v>
       </c>
       <c r="J272" t="n">
-        <v>23.52</v>
+        <v>23.095</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>0.75</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.2828</v>
+        <v>-0.265</v>
       </c>
       <c r="J273" t="n">
-        <v>-7.07</v>
+        <v>-6.625</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>0.7</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3293</v>
+        <v>-0.3131</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.2325</v>
+        <v>-7.8275</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4108</v>
+        <v>-0.4002</v>
       </c>
       <c r="J275" t="n">
-        <v>-10.27</v>
+        <v>-10.005</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.55</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4638</v>
+        <v>-0.4586</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.595</v>
+        <v>-11.465</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.79</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4462</v>
+        <v>1.4741</v>
       </c>
       <c r="J277" t="n">
-        <v>36.155</v>
+        <v>36.8525</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>1.56</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1552</v>
+        <v>1.1697</v>
       </c>
       <c r="J278" t="n">
-        <v>28.88</v>
+        <v>29.2425</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>1.17</v>
       </c>
       <c r="I279" t="n">
-        <v>0.4558</v>
+        <v>0.4251</v>
       </c>
       <c r="J279" t="n">
-        <v>11.395</v>
+        <v>10.6275</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>1.16</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4326</v>
+        <v>0.4014</v>
       </c>
       <c r="J280" t="n">
-        <v>10.815</v>
+        <v>10.035</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>1.12</v>
       </c>
       <c r="I281" t="n">
-        <v>0.3357</v>
+        <v>0.3037</v>
       </c>
       <c r="J281" t="n">
-        <v>8.3925</v>
+        <v>7.5925</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.15</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4223</v>
+        <v>0.3777</v>
       </c>
       <c r="J282" t="n">
-        <v>9.2906</v>
+        <v>8.3094</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.86</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1698</v>
+        <v>-0.154</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.7356</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.78</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2509</v>
+        <v>-0.2344</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.5198</v>
+        <v>-5.1568</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.57</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4408</v>
+        <v>-0.4329</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.6976</v>
+        <v>-9.5238</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.48</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5195</v>
+        <v>-0.5208</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.429</v>
+        <v>-11.4576</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.55</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1387</v>
+        <v>1.1534</v>
       </c>
       <c r="J287" t="n">
-        <v>25.0514</v>
+        <v>25.3748</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.53</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1127</v>
+        <v>1.127</v>
       </c>
       <c r="J288" t="n">
-        <v>24.4794</v>
+        <v>24.794</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.43</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9677</v>
       </c>
       <c r="J289" t="n">
-        <v>21.3246</v>
+        <v>21.2894</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.21</v>
       </c>
       <c r="I290" t="n">
-        <v>0.542</v>
+        <v>0.5141</v>
       </c>
       <c r="J290" t="n">
-        <v>11.924</v>
+        <v>11.3102</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>1.2</v>
       </c>
       <c r="I291" t="n">
-        <v>0.52</v>
+        <v>0.4913</v>
       </c>
       <c r="J291" t="n">
-        <v>11.44</v>
+        <v>10.8086</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.39</v>
       </c>
       <c r="I292" t="n">
-        <v>0.7388</v>
+        <v>0.6845</v>
       </c>
       <c r="J292" t="n">
-        <v>18.47</v>
+        <v>17.1125</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.03</v>
       </c>
       <c r="I293" t="n">
-        <v>0.101</v>
+        <v>0.0745</v>
       </c>
       <c r="J293" t="n">
-        <v>2.525</v>
+        <v>1.8625</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.99</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0249</v>
+        <v>-0.018</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.82</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2317</v>
+        <v>-0.2113</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.7925</v>
+        <v>-5.2825</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3191</v>
+        <v>-0.3023</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.9775</v>
+        <v>-7.5575</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.59</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2491</v>
+        <v>1.2689</v>
       </c>
       <c r="J297" t="n">
-        <v>31.2275</v>
+        <v>31.7225</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.16</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4667</v>
+        <v>0.4277</v>
       </c>
       <c r="J298" t="n">
-        <v>11.6675</v>
+        <v>10.6925</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3961</v>
+        <v>0.3578</v>
       </c>
       <c r="J299" t="n">
-        <v>9.9025</v>
+        <v>8.945</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.06</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2137</v>
+        <v>0.1833</v>
       </c>
       <c r="J300" t="n">
-        <v>5.3425</v>
+        <v>4.5825</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.9563</v>
+        <v>-0.9503</v>
       </c>
       <c r="J301" t="n">
-        <v>-23.9075</v>
+        <v>-23.7575</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>2.38</v>
       </c>
       <c r="I302" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J302" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.78</v>
       </c>
       <c r="I303" t="n">
-        <v>1.3825</v>
+        <v>1.4136</v>
       </c>
       <c r="J303" t="n">
-        <v>23.5025</v>
+        <v>24.0312</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.62</v>
       </c>
       <c r="I304" t="n">
-        <v>1.1955</v>
+        <v>1.2214</v>
       </c>
       <c r="J304" t="n">
-        <v>20.3235</v>
+        <v>20.7638</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.51</v>
       </c>
       <c r="I305" t="n">
-        <v>1.0562</v>
+        <v>1.0772</v>
       </c>
       <c r="J305" t="n">
-        <v>17.9554</v>
+        <v>18.3124</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.38</v>
       </c>
       <c r="I306" t="n">
-        <v>0.8389</v>
+        <v>0.8335</v>
       </c>
       <c r="J306" t="n">
-        <v>14.2613</v>
+        <v>14.1695</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>0.92</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0068</v>
+        <v>0.0648</v>
       </c>
       <c r="J307" t="n">
-        <v>-0.1156</v>
+        <v>1.1016</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.42</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.5364</v>
       </c>
       <c r="J308" t="n">
-        <v>-9.0746</v>
+        <v>-9.1188</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.4</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.5516</v>
+        <v>-0.556</v>
       </c>
       <c r="J309" t="n">
-        <v>-9.3772</v>
+        <v>-9.452</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.4</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5516</v>
+        <v>-0.556</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.3772</v>
+        <v>-9.452</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.35</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5967</v>
+        <v>-0.6065</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.1439</v>
+        <v>-10.3105</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.8</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4453</v>
+        <v>1.473</v>
       </c>
       <c r="J312" t="n">
-        <v>31.7966</v>
+        <v>32.406</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.62</v>
       </c>
       <c r="I313" t="n">
-        <v>1.2224</v>
+        <v>1.2399</v>
       </c>
       <c r="J313" t="n">
-        <v>26.8928</v>
+        <v>27.2778</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.44</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9836</v>
       </c>
       <c r="J314" t="n">
-        <v>21.5908</v>
+        <v>21.6392</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.27</v>
       </c>
       <c r="I315" t="n">
-        <v>0.663</v>
+        <v>0.6412</v>
       </c>
       <c r="J315" t="n">
-        <v>14.586</v>
+        <v>14.1064</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>1</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.0698</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J316" t="n">
-        <v>-1.5356</v>
+        <v>-1.4982</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>0.97</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.0162</v>
+        <v>-0.0035</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.3564</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>0.75</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.2725</v>
+        <v>-0.2582</v>
       </c>
       <c r="J318" t="n">
-        <v>-5.995</v>
+        <v>-5.6804</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.64</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3707</v>
+        <v>-0.3583</v>
       </c>
       <c r="J319" t="n">
-        <v>-8.1554</v>
+        <v>-7.8826</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.59</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4152</v>
+        <v>-0.4053</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.134399999999999</v>
+        <v>-8.916600000000001</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.57</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4329</v>
+        <v>-0.4244</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.5238</v>
+        <v>-9.3368</v>
       </c>
     </row>
   </sheetData>
